--- a/raw/INT.xlsx
+++ b/raw/INT.xlsx
@@ -1299,19 +1299,19 @@
         <v>347.4</v>
       </c>
       <c r="O8" t="n">
-        <v>347.4</v>
+        <v>362.6</v>
       </c>
       <c r="P8" t="n">
-        <v>347.4</v>
+        <v>362.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>347.4</v>
+        <v>362.6</v>
       </c>
       <c r="R8" t="n">
-        <v>308.5</v>
+        <v>320</v>
       </c>
       <c r="S8" t="n">
-        <v>308.5</v>
+        <v>320</v>
       </c>
       <c r="T8" t="n">
         <v>362.6</v>
@@ -1453,13 +1453,13 @@
         <v>362.6</v>
       </c>
       <c r="O9" t="n">
-        <v>362.6</v>
+        <v>347.4</v>
       </c>
       <c r="P9" t="n">
-        <v>362.6</v>
+        <v>347.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>362.6</v>
+        <v>347.4</v>
       </c>
       <c r="R9" t="n">
         <v>320</v>
@@ -1800,10 +1800,10 @@
         <v>300</v>
       </c>
       <c r="AB11" t="n">
-        <v>300</v>
+        <v>369.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>369.6</v>
+        <v>318.6</v>
       </c>
       <c r="AD11" t="n">
         <v>318.6</v>
@@ -1948,13 +1948,13 @@
         <v>441</v>
       </c>
       <c r="Z12" t="n">
-        <v>300</v>
+        <v>352.38</v>
       </c>
       <c r="AA12" t="n">
         <v>300</v>
       </c>
       <c r="AB12" t="n">
-        <v>300</v>
+        <v>441</v>
       </c>
       <c r="AC12" t="n">
         <v>441</v>
@@ -2108,10 +2108,10 @@
         <v>300</v>
       </c>
       <c r="AB13" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="AC13" t="n">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="AD13" t="n">
         <v>441</v>
@@ -2273,13 +2273,13 @@
         <v>300.76</v>
       </c>
       <c r="O15" t="n">
-        <v>300.76</v>
+        <v>269.58</v>
       </c>
       <c r="P15" t="n">
-        <v>300.76</v>
+        <v>323.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>375.31</v>
+        <v>379.34</v>
       </c>
       <c r="R15" t="n">
         <v>402.96</v>
@@ -2288,61 +2288,61 @@
         <v>402.96</v>
       </c>
       <c r="T15" t="n">
-        <v>441.89</v>
+        <v>431.82</v>
       </c>
       <c r="U15" t="n">
-        <v>465.56</v>
+        <v>458.44</v>
       </c>
       <c r="V15" t="n">
-        <v>487.94</v>
+        <v>463.33</v>
       </c>
       <c r="W15" t="n">
-        <v>544.71</v>
+        <v>513.6</v>
       </c>
       <c r="X15" t="n">
-        <v>517.8099999999999</v>
+        <v>508.85</v>
       </c>
       <c r="Y15" t="n">
-        <v>515.3200000000001</v>
+        <v>500.07</v>
       </c>
       <c r="Z15" t="n">
-        <v>515.39</v>
+        <v>483.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>495.04</v>
+        <v>506.22</v>
       </c>
       <c r="AB15" t="n">
-        <v>512.11</v>
+        <v>515.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>547.5</v>
+        <v>542.58</v>
       </c>
       <c r="AD15" t="n">
         <v>547.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>547.5</v>
+        <v>540.96</v>
       </c>
       <c r="AF15" t="n">
-        <v>547.5</v>
+        <v>525.61</v>
       </c>
       <c r="AG15" t="n">
-        <v>547.5</v>
+        <v>528.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>495.17</v>
+        <v>464.16</v>
       </c>
       <c r="AI15" t="n">
-        <v>434.9</v>
+        <v>425.59</v>
       </c>
       <c r="AJ15" t="n">
-        <v>404.98</v>
+        <v>402.96</v>
       </c>
       <c r="AK15" t="n">
         <v>402.96</v>
       </c>
       <c r="AL15" t="n">
-        <v>402.96</v>
+        <v>419.01</v>
       </c>
       <c r="AM15" t="n">
         <v>402.96</v>
@@ -2360,7 +2360,7 @@
         <v>402.96</v>
       </c>
       <c r="AR15" t="n">
-        <v>404.69</v>
+        <v>402.96</v>
       </c>
       <c r="AS15" t="n">
         <v>402.96</v>
@@ -2372,13 +2372,13 @@
         <v>300.76</v>
       </c>
       <c r="AV15" t="n">
-        <v>300.76</v>
+        <v>291.6</v>
       </c>
       <c r="AW15" t="n">
         <v>300.76</v>
       </c>
       <c r="AX15" t="n">
-        <v>300.76</v>
+        <v>300.74</v>
       </c>
     </row>
     <row r="16">
@@ -2425,13 +2425,13 @@
         <v>150.32</v>
       </c>
       <c r="O16" t="n">
-        <v>166.01</v>
+        <v>197.26</v>
       </c>
       <c r="P16" t="n">
-        <v>197.26</v>
+        <v>204.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>247.24</v>
+        <v>252.58</v>
       </c>
       <c r="R16" t="n">
         <v>252.58</v>
@@ -2440,52 +2440,52 @@
         <v>252.58</v>
       </c>
       <c r="T16" t="n">
-        <v>278.86</v>
+        <v>252.58</v>
       </c>
       <c r="U16" t="n">
-        <v>307.88</v>
+        <v>278.8</v>
       </c>
       <c r="V16" t="n">
+        <v>321.27</v>
+      </c>
+      <c r="W16" t="n">
+        <v>357.63</v>
+      </c>
+      <c r="X16" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="Y16" t="n">
         <v>332.88</v>
       </c>
-      <c r="W16" t="n">
-        <v>363.88</v>
-      </c>
-      <c r="X16" t="n">
-        <v>358.4</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>354.05</v>
-      </c>
       <c r="Z16" t="n">
-        <v>338.36</v>
+        <v>332.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>332.88</v>
+        <v>284.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>350.05</v>
+        <v>310.48</v>
       </c>
       <c r="AC16" t="n">
-        <v>365</v>
+        <v>364.91</v>
       </c>
       <c r="AD16" t="n">
         <v>365</v>
       </c>
       <c r="AE16" t="n">
-        <v>365</v>
+        <v>361.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>365</v>
+        <v>357.68</v>
       </c>
       <c r="AG16" t="n">
-        <v>365</v>
+        <v>358.56</v>
       </c>
       <c r="AH16" t="n">
-        <v>332.88</v>
+        <v>328.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>278.86</v>
+        <v>252.58</v>
       </c>
       <c r="AJ16" t="n">
         <v>252.58</v>
@@ -2577,19 +2577,19 @@
         <v>565.02</v>
       </c>
       <c r="O17" t="n">
-        <v>579.26</v>
+        <v>539.23</v>
       </c>
       <c r="P17" t="n">
-        <v>605.29</v>
+        <v>539.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>584.99</v>
+        <v>539.23</v>
       </c>
       <c r="R17" t="n">
-        <v>628.5</v>
+        <v>592.24</v>
       </c>
       <c r="S17" t="n">
-        <v>704.71</v>
+        <v>668.83</v>
       </c>
       <c r="T17" t="n">
         <v>720</v>
@@ -2640,49 +2640,49 @@
         <v>720</v>
       </c>
       <c r="AJ17" t="n">
+        <v>686.58</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>610.79</v>
+      </c>
+      <c r="AL17" t="n">
         <v>720</v>
       </c>
-      <c r="AK17" t="n">
-        <v>645.73</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>713.87</v>
-      </c>
       <c r="AM17" t="n">
-        <v>713.87</v>
+        <v>626.55</v>
       </c>
       <c r="AN17" t="n">
-        <v>646.59</v>
+        <v>611.86</v>
       </c>
       <c r="AO17" t="n">
-        <v>621.4400000000001</v>
+        <v>586.95</v>
       </c>
       <c r="AP17" t="n">
-        <v>660.41</v>
+        <v>626.12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>707.6799999999999</v>
+        <v>676.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>720</v>
+        <v>687.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>713.87</v>
+        <v>654.62</v>
       </c>
       <c r="AT17" t="n">
-        <v>648.49</v>
+        <v>613.97</v>
       </c>
       <c r="AU17" t="n">
-        <v>680.58</v>
+        <v>646.33</v>
       </c>
       <c r="AV17" t="n">
-        <v>649.01</v>
+        <v>623.54</v>
       </c>
       <c r="AW17" t="n">
-        <v>604.3099999999999</v>
+        <v>569.66</v>
       </c>
       <c r="AX17" t="n">
-        <v>575.54</v>
+        <v>540.34</v>
       </c>
     </row>
     <row r="18">
@@ -4629,43 +4629,43 @@
         <v>250</v>
       </c>
       <c r="O33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="P33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="Q33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="R33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="S33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="T33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="U33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="V33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="W33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="X33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="Y33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="Z33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AA33" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB33" t="n">
         <v>260</v>
@@ -4989,112 +4989,112 @@
         <v>430</v>
       </c>
       <c r="O36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="P36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="Q36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="R36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="S36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="T36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="U36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="V36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="W36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="X36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="Y36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="Z36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AA36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AB36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AC36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AD36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AE36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AF36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AG36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AH36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AI36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AJ36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AK36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AL36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AM36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AN36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AO36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AP36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AQ36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AR36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AS36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AT36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AU36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AV36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AW36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
       <c r="AX36" t="n">
-        <v>430</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37">
@@ -5204,28 +5204,28 @@
         <v>254.95</v>
       </c>
       <c r="R38" t="n">
-        <v>261.29</v>
+        <v>254.95</v>
       </c>
       <c r="S38" t="n">
-        <v>268.19</v>
+        <v>254.95</v>
       </c>
       <c r="T38" t="n">
-        <v>268.19</v>
+        <v>254.95</v>
       </c>
       <c r="U38" t="n">
-        <v>268.19</v>
+        <v>254.95</v>
       </c>
       <c r="V38" t="n">
-        <v>268.19</v>
+        <v>254.95</v>
       </c>
       <c r="W38" t="n">
-        <v>268.19</v>
+        <v>254.95</v>
       </c>
       <c r="X38" t="n">
-        <v>268.19</v>
+        <v>254.95</v>
       </c>
       <c r="Y38" t="n">
-        <v>268.19</v>
+        <v>254.95</v>
       </c>
       <c r="Z38" t="n">
         <v>254.95</v>
@@ -5234,67 +5234,67 @@
         <v>254.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>254.95</v>
+        <v>276.86</v>
       </c>
       <c r="AC38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AD38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AE38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AF38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AG38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AH38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AI38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AJ38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AK38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AL38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AM38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AN38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AO38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AP38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AQ38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AR38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AS38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AT38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AU38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AV38" t="n">
-        <v>261.38</v>
+        <v>276.86</v>
       </c>
       <c r="AW38" t="n">
         <v>254.95</v>
@@ -5358,7 +5358,7 @@
         <v>254.95</v>
       </c>
       <c r="R39" t="n">
-        <v>276.86</v>
+        <v>254.95</v>
       </c>
       <c r="S39" t="n">
         <v>276.86</v>
@@ -5382,76 +5382,76 @@
         <v>276.86</v>
       </c>
       <c r="Z39" t="n">
-        <v>254.95</v>
+        <v>276.86</v>
       </c>
       <c r="AA39" t="n">
         <v>254.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AC39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AD39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AE39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AF39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AG39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AH39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AJ39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AK39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AL39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AM39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AN39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AO39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AP39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AQ39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AR39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AS39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AT39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AU39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AV39" t="n">
-        <v>276.86</v>
+        <v>268.19</v>
       </c>
       <c r="AW39" t="n">
-        <v>257.16</v>
+        <v>254.95</v>
       </c>
       <c r="AX39" t="n">
         <v>254.95</v>
@@ -5515,97 +5515,97 @@
         <v>254.95</v>
       </c>
       <c r="S40" t="n">
-        <v>254.95</v>
+        <v>268.19</v>
       </c>
       <c r="T40" t="n">
-        <v>254.95</v>
+        <v>268.19</v>
       </c>
       <c r="U40" t="n">
-        <v>254.95</v>
+        <v>268.19</v>
       </c>
       <c r="V40" t="n">
-        <v>254.95</v>
+        <v>268.19</v>
       </c>
       <c r="W40" t="n">
-        <v>254.95</v>
+        <v>268.19</v>
       </c>
       <c r="X40" t="n">
-        <v>254.95</v>
+        <v>268.19</v>
       </c>
       <c r="Y40" t="n">
-        <v>254.95</v>
+        <v>268.19</v>
       </c>
       <c r="Z40" t="n">
-        <v>254.95</v>
+        <v>268.19</v>
       </c>
       <c r="AA40" t="n">
         <v>254.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AC40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AD40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AE40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AF40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AG40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AH40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AI40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AJ40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AK40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AL40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AM40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AN40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AO40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AP40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AQ40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AR40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AS40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AT40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AU40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AV40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AW40" t="n">
-        <v>261.76</v>
+        <v>254.95</v>
       </c>
       <c r="AX40" t="n">
         <v>254.95</v>
@@ -6171,112 +6171,112 @@
         <v>230</v>
       </c>
       <c r="O45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="P45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="Q45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="R45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="S45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="T45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="U45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="V45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="W45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="X45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="Y45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="Z45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AA45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AB45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AC45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AD45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AE45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AF45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AH45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AI45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AJ45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AK45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AL45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AM45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AO45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AP45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AQ45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AR45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AS45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AT45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AU45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AV45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AW45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AX45" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46">
@@ -6413,7 +6413,7 @@
         <v>284.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>206.89</v>
+        <v>284.2</v>
       </c>
       <c r="AB47" t="n">
         <v>284.2</v>
@@ -7185,19 +7185,19 @@
         <v>122.28</v>
       </c>
       <c r="O53" t="n">
-        <v>122.28</v>
+        <v>151.25</v>
       </c>
       <c r="P53" t="n">
-        <v>122.28</v>
+        <v>187.57</v>
       </c>
       <c r="Q53" t="n">
-        <v>122.28</v>
+        <v>187.57</v>
       </c>
       <c r="R53" t="n">
-        <v>151.25</v>
+        <v>245.04</v>
       </c>
       <c r="S53" t="n">
-        <v>187.57</v>
+        <v>281.36</v>
       </c>
       <c r="T53" t="n">
         <v>400</v>
@@ -7352,10 +7352,10 @@
         <v>180.85</v>
       </c>
       <c r="T54" t="n">
+        <v>199.37</v>
+      </c>
+      <c r="U54" t="n">
         <v>180.85</v>
-      </c>
-      <c r="U54" t="n">
-        <v>242.11</v>
       </c>
       <c r="V54" t="n">
         <v>180.85</v>
@@ -7370,7 +7370,7 @@
         <v>180.85</v>
       </c>
       <c r="Z54" t="n">
-        <v>191.93</v>
+        <v>180.85</v>
       </c>
       <c r="AA54" t="n">
         <v>180.85</v>
@@ -7379,25 +7379,25 @@
         <v>180.85</v>
       </c>
       <c r="AC54" t="n">
-        <v>218.76</v>
+        <v>251.74</v>
       </c>
       <c r="AD54" t="n">
-        <v>214.83</v>
+        <v>251.74</v>
       </c>
       <c r="AE54" t="n">
-        <v>240.04</v>
+        <v>251.74</v>
       </c>
       <c r="AF54" t="n">
-        <v>199.83</v>
+        <v>251.74</v>
       </c>
       <c r="AG54" t="n">
-        <v>204.19</v>
+        <v>180.85</v>
       </c>
       <c r="AH54" t="n">
-        <v>211.64</v>
+        <v>184</v>
       </c>
       <c r="AI54" t="n">
-        <v>201.53</v>
+        <v>180.85</v>
       </c>
       <c r="AJ54" t="n">
         <v>180.85</v>
@@ -7406,22 +7406,22 @@
         <v>180.85</v>
       </c>
       <c r="AL54" t="n">
-        <v>328.29</v>
+        <v>340</v>
       </c>
       <c r="AM54" t="n">
         <v>251.74</v>
       </c>
       <c r="AN54" t="n">
-        <v>180.85</v>
+        <v>197.68</v>
       </c>
       <c r="AO54" t="n">
         <v>180.85</v>
       </c>
       <c r="AP54" t="n">
-        <v>226.01</v>
+        <v>251.63</v>
       </c>
       <c r="AQ54" t="n">
-        <v>242.53</v>
+        <v>251.74</v>
       </c>
       <c r="AR54" t="n">
         <v>180.85</v>
@@ -7436,10 +7436,10 @@
         <v>180.85</v>
       </c>
       <c r="AV54" t="n">
-        <v>207.63</v>
+        <v>180.85</v>
       </c>
       <c r="AW54" t="n">
-        <v>200.99</v>
+        <v>180.85</v>
       </c>
       <c r="AX54" t="n">
         <v>180.85</v>
@@ -7491,46 +7491,46 @@
         <v>82.5</v>
       </c>
       <c r="O55" t="n">
-        <v>95.3</v>
+        <v>82.5</v>
       </c>
       <c r="P55" t="n">
-        <v>115.64</v>
+        <v>82.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>149.95</v>
+        <v>108.58</v>
       </c>
       <c r="R55" t="n">
-        <v>164.14</v>
+        <v>108.27</v>
       </c>
       <c r="S55" t="n">
+        <v>118.29</v>
+      </c>
+      <c r="T55" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="U55" t="n">
+        <v>107.03</v>
+      </c>
+      <c r="V55" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="W55" t="n">
+        <v>137.79</v>
+      </c>
+      <c r="X55" t="n">
+        <v>143.74</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>123.02</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>159.57</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>150.09</v>
+      </c>
+      <c r="AB55" t="n">
         <v>165</v>
-      </c>
-      <c r="T55" t="n">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="U55" t="n">
-        <v>165</v>
-      </c>
-      <c r="V55" t="n">
-        <v>165</v>
-      </c>
-      <c r="W55" t="n">
-        <v>165</v>
-      </c>
-      <c r="X55" t="n">
-        <v>165</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>164.89</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>165</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>162.1</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>159.64</v>
       </c>
       <c r="AC55" t="n">
         <v>165</v>
@@ -7554,7 +7554,7 @@
         <v>165</v>
       </c>
       <c r="AJ55" t="n">
-        <v>165</v>
+        <v>164.26</v>
       </c>
       <c r="AK55" t="n">
         <v>165</v>
@@ -7569,7 +7569,7 @@
         <v>165</v>
       </c>
       <c r="AO55" t="n">
-        <v>125.67</v>
+        <v>165</v>
       </c>
       <c r="AP55" t="n">
         <v>165</v>
@@ -7587,7 +7587,7 @@
         <v>165</v>
       </c>
       <c r="AU55" t="n">
-        <v>165</v>
+        <v>108.96</v>
       </c>
       <c r="AV55" t="n">
         <v>82.5</v>
@@ -7596,7 +7596,7 @@
         <v>82.5</v>
       </c>
       <c r="AX55" t="n">
-        <v>122.39</v>
+        <v>135.83</v>
       </c>
     </row>
     <row r="56">
@@ -7645,46 +7645,46 @@
         <v>165</v>
       </c>
       <c r="O56" t="n">
-        <v>190.59</v>
+        <v>165</v>
       </c>
       <c r="P56" t="n">
-        <v>231.28</v>
+        <v>165</v>
       </c>
       <c r="Q56" t="n">
-        <v>299.91</v>
+        <v>217.17</v>
       </c>
       <c r="R56" t="n">
-        <v>328.27</v>
+        <v>216.54</v>
       </c>
       <c r="S56" t="n">
+        <v>236.59</v>
+      </c>
+      <c r="T56" t="n">
+        <v>165</v>
+      </c>
+      <c r="U56" t="n">
+        <v>214.06</v>
+      </c>
+      <c r="V56" t="n">
+        <v>233.36</v>
+      </c>
+      <c r="W56" t="n">
+        <v>275.59</v>
+      </c>
+      <c r="X56" t="n">
+        <v>287.48</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>246.04</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>319.14</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>300.19</v>
+      </c>
+      <c r="AB56" t="n">
         <v>330</v>
-      </c>
-      <c r="T56" t="n">
-        <v>192.3</v>
-      </c>
-      <c r="U56" t="n">
-        <v>330</v>
-      </c>
-      <c r="V56" t="n">
-        <v>330</v>
-      </c>
-      <c r="W56" t="n">
-        <v>330</v>
-      </c>
-      <c r="X56" t="n">
-        <v>330</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>329.77</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>330</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>324.2</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>319.28</v>
       </c>
       <c r="AC56" t="n">
         <v>330</v>
@@ -7708,7 +7708,7 @@
         <v>330</v>
       </c>
       <c r="AJ56" t="n">
-        <v>330</v>
+        <v>328.53</v>
       </c>
       <c r="AK56" t="n">
         <v>330</v>
@@ -7723,7 +7723,7 @@
         <v>330</v>
       </c>
       <c r="AO56" t="n">
-        <v>251.34</v>
+        <v>330</v>
       </c>
       <c r="AP56" t="n">
         <v>330</v>
@@ -7741,7 +7741,7 @@
         <v>330</v>
       </c>
       <c r="AU56" t="n">
-        <v>330</v>
+        <v>217.91</v>
       </c>
       <c r="AV56" t="n">
         <v>165</v>
@@ -7750,7 +7750,7 @@
         <v>165</v>
       </c>
       <c r="AX56" t="n">
-        <v>244.78</v>
+        <v>271.66</v>
       </c>
     </row>
     <row r="57">
@@ -8616,7 +8616,7 @@
         <v>926.1</v>
       </c>
       <c r="P65" t="n">
-        <v>926.1</v>
+        <v>776.1</v>
       </c>
       <c r="Q65" t="n">
         <v>926.1</v>
@@ -9537,112 +9537,112 @@
         <v>10140.11</v>
       </c>
       <c r="O73" t="n">
-        <v>10294.28</v>
+        <v>10279.9</v>
       </c>
       <c r="P73" t="n">
-        <v>10422.59</v>
+        <v>10237.09</v>
       </c>
       <c r="Q73" t="n">
-        <v>10629.76</v>
+        <v>10569.55</v>
       </c>
       <c r="R73" t="n">
-        <v>10806.03</v>
+        <v>10714.21</v>
       </c>
       <c r="S73" t="n">
-        <v>10928.05</v>
+        <v>10892.34</v>
       </c>
       <c r="T73" t="n">
-        <v>11400.01</v>
+        <v>11376.23</v>
       </c>
       <c r="U73" t="n">
-        <v>11734.93</v>
+        <v>11498.56</v>
       </c>
       <c r="V73" t="n">
-        <v>11814.45</v>
+        <v>11668.27</v>
       </c>
       <c r="W73" t="n">
-        <v>11906.22</v>
+        <v>11822.24</v>
       </c>
       <c r="X73" t="n">
-        <v>11883.84</v>
+        <v>11818.51</v>
       </c>
       <c r="Y73" t="n">
-        <v>11876.66</v>
+        <v>11749.64</v>
       </c>
       <c r="Z73" t="n">
-        <v>11418.07</v>
+        <v>11476.03</v>
       </c>
       <c r="AA73" t="n">
-        <v>11295.15</v>
+        <v>11334.44</v>
       </c>
       <c r="AB73" t="n">
-        <v>11448.04</v>
+        <v>11759.85</v>
       </c>
       <c r="AC73" t="n">
-        <v>11868.9</v>
+        <v>11921.87</v>
       </c>
       <c r="AD73" t="n">
-        <v>11864.97</v>
+        <v>11926.88</v>
       </c>
       <c r="AE73" t="n">
-        <v>11890.18</v>
+        <v>11916.37</v>
       </c>
       <c r="AF73" t="n">
-        <v>11849.97</v>
+        <v>11897.67</v>
       </c>
       <c r="AG73" t="n">
-        <v>11854.33</v>
+        <v>11830.72</v>
       </c>
       <c r="AH73" t="n">
-        <v>11831.07</v>
+        <v>11793.14</v>
       </c>
       <c r="AI73" t="n">
-        <v>11802.93</v>
+        <v>11771.66</v>
       </c>
       <c r="AJ73" t="n">
-        <v>11726.05</v>
+        <v>11713.4</v>
       </c>
       <c r="AK73" t="n">
-        <v>11649.76</v>
+        <v>11639.82</v>
       </c>
       <c r="AL73" t="n">
-        <v>11865.34</v>
+        <v>11924.23</v>
       </c>
       <c r="AM73" t="n">
-        <v>11788.79</v>
+        <v>11726.47</v>
       </c>
       <c r="AN73" t="n">
-        <v>11650.62</v>
+        <v>11657.72</v>
       </c>
       <c r="AO73" t="n">
-        <v>11414.08</v>
+        <v>11522.58</v>
       </c>
       <c r="AP73" t="n">
-        <v>11526.56</v>
+        <v>11542.89</v>
       </c>
       <c r="AQ73" t="n">
-        <v>11457.2</v>
+        <v>11460.03</v>
       </c>
       <c r="AR73" t="n">
-        <v>11363.94</v>
+        <v>11354.51</v>
       </c>
       <c r="AS73" t="n">
-        <v>10972.31</v>
+        <v>10938.06</v>
       </c>
       <c r="AT73" t="n">
-        <v>10786.04</v>
+        <v>10776.52</v>
       </c>
       <c r="AU73" t="n">
-        <v>10675.93</v>
+        <v>10498.55</v>
       </c>
       <c r="AV73" t="n">
-        <v>10423.64</v>
+        <v>10387.23</v>
       </c>
       <c r="AW73" t="n">
-        <v>10346.17</v>
+        <v>10307.36</v>
       </c>
       <c r="AX73" t="n">
-        <v>10407.91</v>
+        <v>10438.01</v>
       </c>
     </row>
     <row r="74">
@@ -9689,112 +9689,112 @@
         <v>10944.96</v>
       </c>
       <c r="O74" t="n">
-        <v>10809.07</v>
+        <v>10551.38</v>
       </c>
       <c r="P74" t="n">
-        <v>10911.3</v>
+        <v>10682.35</v>
       </c>
       <c r="Q74" t="n">
-        <v>11411.13</v>
+        <v>11185.09</v>
       </c>
       <c r="R74" t="n">
-        <v>11792.22</v>
+        <v>11568.78</v>
       </c>
       <c r="S74" t="n">
-        <v>12154.93</v>
+        <v>11935.88</v>
       </c>
       <c r="T74" t="n">
-        <v>12396.14</v>
+        <v>12178.59</v>
       </c>
       <c r="U74" t="n">
-        <v>12659.15</v>
+        <v>12443.32</v>
       </c>
       <c r="V74" t="n">
-        <v>12840.12</v>
+        <v>12625.87</v>
       </c>
       <c r="W74" t="n">
-        <v>12913.06</v>
+        <v>12699.41</v>
       </c>
       <c r="X74" t="n">
-        <v>12943.67</v>
+        <v>12731.18</v>
       </c>
       <c r="Y74" t="n">
-        <v>12921.88</v>
+        <v>12709.83</v>
       </c>
       <c r="Z74" t="n">
-        <v>12740.85</v>
+        <v>12525.76</v>
       </c>
       <c r="AA74" t="n">
-        <v>12664.79</v>
+        <v>12449.6</v>
       </c>
       <c r="AB74" t="n">
-        <v>12980.27</v>
+        <v>12767.26</v>
       </c>
       <c r="AC74" t="n">
-        <v>13420.87</v>
+        <v>13210.76</v>
       </c>
       <c r="AD74" t="n">
-        <v>13448.06</v>
+        <v>13239.42</v>
       </c>
       <c r="AE74" t="n">
-        <v>13446.67</v>
+        <v>13237.95</v>
       </c>
       <c r="AF74" t="n">
-        <v>13381.77</v>
+        <v>13171.78</v>
       </c>
       <c r="AG74" t="n">
-        <v>13409.77</v>
+        <v>13201.48</v>
       </c>
       <c r="AH74" t="n">
-        <v>13234.73</v>
+        <v>13025.46</v>
       </c>
       <c r="AI74" t="n">
-        <v>13129.87</v>
+        <v>12918.78</v>
       </c>
       <c r="AJ74" t="n">
-        <v>12935.28</v>
+        <v>12722.83</v>
       </c>
       <c r="AK74" t="n">
-        <v>12782.92</v>
+        <v>12568.33</v>
       </c>
       <c r="AL74" t="n">
-        <v>12990.29</v>
+        <v>12777.81</v>
       </c>
       <c r="AM74" t="n">
-        <v>12947.98</v>
+        <v>12734.42</v>
       </c>
       <c r="AN74" t="n">
-        <v>12822.89</v>
+        <v>12609.03</v>
       </c>
       <c r="AO74" t="n">
-        <v>12753.49</v>
+        <v>12539.68</v>
       </c>
       <c r="AP74" t="n">
-        <v>12659.46</v>
+        <v>12444.73</v>
       </c>
       <c r="AQ74" t="n">
-        <v>12633.44</v>
+        <v>12418.55</v>
       </c>
       <c r="AR74" t="n">
-        <v>12536.68</v>
+        <v>12321.63</v>
       </c>
       <c r="AS74" t="n">
-        <v>12353.7</v>
+        <v>12138.7</v>
       </c>
       <c r="AT74" t="n">
-        <v>12168.41</v>
+        <v>11951.23</v>
       </c>
       <c r="AU74" t="n">
-        <v>11921.03</v>
+        <v>11701.91</v>
       </c>
       <c r="AV74" t="n">
-        <v>11704.19</v>
+        <v>11483.01</v>
       </c>
       <c r="AW74" t="n">
-        <v>11497.84</v>
+        <v>11274.89</v>
       </c>
       <c r="AX74" t="n">
-        <v>11301.14</v>
+        <v>11074.84</v>
       </c>
     </row>
     <row r="75">
@@ -10451,19 +10451,19 @@
         <v>130</v>
       </c>
       <c r="O81" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>112.5</v>
+        <v>105.38</v>
       </c>
       <c r="S81" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="T81" t="n">
         <v>112.5</v>
@@ -10472,46 +10472,46 @@
         <v>112.5</v>
       </c>
       <c r="V81" t="n">
+        <v>105</v>
+      </c>
+      <c r="W81" t="n">
+        <v>95</v>
+      </c>
+      <c r="X81" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>145</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>105</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>105</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>105</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>105</v>
+      </c>
+      <c r="AI81" t="n">
         <v>100</v>
-      </c>
-      <c r="W81" t="n">
-        <v>110</v>
-      </c>
-      <c r="X81" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>110</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA81" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC81" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AE81" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AF81" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AG81" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AH81" t="n">
-        <v>100</v>
-      </c>
-      <c r="AI81" t="n">
-        <v>112.5</v>
       </c>
       <c r="AJ81" t="n">
         <v>100</v>
@@ -10614,10 +10614,10 @@
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>112.5</v>
+        <v>105.38</v>
       </c>
       <c r="S82" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="T82" t="n">
         <v>112.5</v>
@@ -10626,46 +10626,46 @@
         <v>112.5</v>
       </c>
       <c r="V82" t="n">
+        <v>105</v>
+      </c>
+      <c r="W82" t="n">
+        <v>95</v>
+      </c>
+      <c r="X82" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>145</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>105</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>105</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>105</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>105</v>
+      </c>
+      <c r="AI82" t="n">
         <v>100</v>
-      </c>
-      <c r="W82" t="n">
-        <v>110</v>
-      </c>
-      <c r="X82" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>110</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>100</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>112.5</v>
       </c>
       <c r="AJ82" t="n">
         <v>100</v>
@@ -10768,10 +10768,10 @@
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>112.5</v>
+        <v>105.38</v>
       </c>
       <c r="S83" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="T83" t="n">
         <v>112.5</v>
@@ -10780,46 +10780,46 @@
         <v>112.5</v>
       </c>
       <c r="V83" t="n">
+        <v>105</v>
+      </c>
+      <c r="W83" t="n">
+        <v>95</v>
+      </c>
+      <c r="X83" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>145</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>105</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>105</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>105</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>105</v>
+      </c>
+      <c r="AI83" t="n">
         <v>100</v>
-      </c>
-      <c r="W83" t="n">
-        <v>110</v>
-      </c>
-      <c r="X83" t="n">
-        <v>110</v>
-      </c>
-      <c r="Y83" t="n">
-        <v>110</v>
-      </c>
-      <c r="Z83" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA83" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC83" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD83" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AE83" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AF83" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AG83" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AH83" t="n">
-        <v>100</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>112.5</v>
       </c>
       <c r="AJ83" t="n">
         <v>100</v>
@@ -10922,10 +10922,10 @@
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>112.5</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="T84" t="n">
         <v>112.5</v>
@@ -10934,46 +10934,46 @@
         <v>112.5</v>
       </c>
       <c r="V84" t="n">
+        <v>105</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>105</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>105</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>110</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>105</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>105</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>105</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>105</v>
+      </c>
+      <c r="AI84" t="n">
         <v>100</v>
-      </c>
-      <c r="W84" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC84" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AF84" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AG84" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="AH84" t="n">
-        <v>100</v>
-      </c>
-      <c r="AI84" t="n">
-        <v>112.5</v>
       </c>
       <c r="AJ84" t="n">
         <v>100</v>
@@ -11276,7 +11276,7 @@
         <v>52.3</v>
       </c>
       <c r="P87" t="n">
-        <v>52.3</v>
+        <v>39.23</v>
       </c>
       <c r="Q87" t="n">
         <v>52.3</v>
@@ -11430,7 +11430,7 @@
         <v>52.3</v>
       </c>
       <c r="P88" t="n">
-        <v>52.3</v>
+        <v>39.23</v>
       </c>
       <c r="Q88" t="n">
         <v>52.3</v>
@@ -13115,7 +13115,7 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -13133,13 +13133,13 @@
         <v>100</v>
       </c>
       <c r="W101" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="X101" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="Y101" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Z101" t="n">
         <v>0</v>
@@ -13148,7 +13148,7 @@
         <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>104.92</v>
       </c>
       <c r="AC101" t="n">
         <v>100</v>
@@ -13157,25 +13157,25 @@
         <v>100</v>
       </c>
       <c r="AE101" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="AF101" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AG101" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AH101" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AI101" t="n">
-        <v>57.67</v>
+        <v>100.85</v>
       </c>
       <c r="AJ101" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK101" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="AL101" t="n">
         <v>100</v>
@@ -13202,10 +13202,10 @@
         <v>100</v>
       </c>
       <c r="AT101" t="n">
-        <v>93.97</v>
+        <v>100</v>
       </c>
       <c r="AU101" t="n">
-        <v>100</v>
+        <v>82.84</v>
       </c>
       <c r="AV101" t="n">
         <v>0</v>
@@ -13287,13 +13287,13 @@
         <v>100</v>
       </c>
       <c r="W102" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="X102" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="Y102" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Z102" t="n">
         <v>0</v>
@@ -13311,25 +13311,25 @@
         <v>100</v>
       </c>
       <c r="AE102" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="AF102" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AG102" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AH102" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AI102" t="n">
-        <v>0</v>
+        <v>100.85</v>
       </c>
       <c r="AJ102" t="n">
         <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="AL102" t="n">
         <v>100</v>
@@ -13356,10 +13356,10 @@
         <v>100</v>
       </c>
       <c r="AT102" t="n">
-        <v>93.97</v>
+        <v>100</v>
       </c>
       <c r="AU102" t="n">
-        <v>100</v>
+        <v>82.84</v>
       </c>
       <c r="AV102" t="n">
         <v>0</v>
@@ -13441,13 +13441,13 @@
         <v>100</v>
       </c>
       <c r="W103" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="X103" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="Y103" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Z103" t="n">
         <v>0</v>
@@ -13465,16 +13465,16 @@
         <v>100</v>
       </c>
       <c r="AE103" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="AF103" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AG103" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AH103" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
@@ -13483,7 +13483,7 @@
         <v>0</v>
       </c>
       <c r="AK103" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="AL103" t="n">
         <v>100</v>
@@ -13510,10 +13510,10 @@
         <v>100</v>
       </c>
       <c r="AT103" t="n">
-        <v>93.97</v>
+        <v>100</v>
       </c>
       <c r="AU103" t="n">
-        <v>100</v>
+        <v>82.84</v>
       </c>
       <c r="AV103" t="n">
         <v>0</v>
@@ -13583,7 +13583,7 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
         <v>0</v>
@@ -13619,16 +13619,16 @@
         <v>100</v>
       </c>
       <c r="AE104" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="AF104" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AG104" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -13637,7 +13637,7 @@
         <v>0</v>
       </c>
       <c r="AK104" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="AL104" t="n">
         <v>100</v>
@@ -13664,10 +13664,10 @@
         <v>100</v>
       </c>
       <c r="AT104" t="n">
-        <v>93.97</v>
+        <v>100</v>
       </c>
       <c r="AU104" t="n">
-        <v>100</v>
+        <v>82.84</v>
       </c>
       <c r="AV104" t="n">
         <v>0</v>
@@ -13737,7 +13737,7 @@
         <v>0</v>
       </c>
       <c r="S105" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="AK105" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="AL105" t="n">
         <v>100</v>
@@ -13818,10 +13818,10 @@
         <v>100</v>
       </c>
       <c r="AT105" t="n">
-        <v>93.97</v>
+        <v>100</v>
       </c>
       <c r="AU105" t="n">
-        <v>100</v>
+        <v>82.84</v>
       </c>
       <c r="AV105" t="n">
         <v>0</v>
@@ -14396,55 +14396,55 @@
         <v>57.14</v>
       </c>
       <c r="P110" t="n">
-        <v>57.14</v>
+        <v>114.29</v>
       </c>
       <c r="Q110" t="n">
-        <v>57.14</v>
+        <v>114.29</v>
       </c>
       <c r="R110" t="n">
-        <v>57.14</v>
+        <v>171.43</v>
       </c>
       <c r="S110" t="n">
-        <v>57.14</v>
+        <v>171.43</v>
       </c>
       <c r="T110" t="n">
-        <v>57.14</v>
+        <v>171.43</v>
       </c>
       <c r="U110" t="n">
-        <v>60.67</v>
+        <v>171.43</v>
       </c>
       <c r="V110" t="n">
-        <v>114.29</v>
+        <v>171.43</v>
       </c>
       <c r="W110" t="n">
-        <v>114.29</v>
+        <v>171.43</v>
       </c>
       <c r="X110" t="n">
-        <v>114.29</v>
+        <v>171.43</v>
       </c>
       <c r="Y110" t="n">
-        <v>114.29</v>
+        <v>171.43</v>
       </c>
       <c r="Z110" t="n">
-        <v>114.29</v>
+        <v>171.43</v>
       </c>
       <c r="AA110" t="n">
-        <v>114.29</v>
+        <v>171.43</v>
       </c>
       <c r="AB110" t="n">
         <v>171.43</v>
       </c>
       <c r="AC110" t="n">
-        <v>171.43</v>
+        <v>193.91</v>
       </c>
       <c r="AD110" t="n">
-        <v>171.43</v>
+        <v>193.91</v>
       </c>
       <c r="AE110" t="n">
-        <v>171.43</v>
+        <v>193.91</v>
       </c>
       <c r="AF110" t="n">
-        <v>171.43</v>
+        <v>181.67</v>
       </c>
       <c r="AG110" t="n">
         <v>171.43</v>
@@ -14468,16 +14468,16 @@
         <v>193.91</v>
       </c>
       <c r="AN110" t="n">
-        <v>171.43</v>
+        <v>174.37</v>
       </c>
       <c r="AO110" t="n">
         <v>171.43</v>
       </c>
       <c r="AP110" t="n">
-        <v>174.37</v>
+        <v>192.03</v>
       </c>
       <c r="AQ110" t="n">
-        <v>174.37</v>
+        <v>193.91</v>
       </c>
       <c r="AR110" t="n">
         <v>171.43</v>
@@ -14556,34 +14556,34 @@
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB111" t="n">
         <v>100</v>
@@ -14719,7 +14719,7 @@
         <v>100</v>
       </c>
       <c r="U112" t="n">
-        <v>106.18</v>
+        <v>100</v>
       </c>
       <c r="V112" t="n">
         <v>100</v>
@@ -14743,16 +14743,16 @@
         <v>100</v>
       </c>
       <c r="AC112" t="n">
-        <v>100</v>
+        <v>139.34</v>
       </c>
       <c r="AD112" t="n">
-        <v>100</v>
+        <v>139.34</v>
       </c>
       <c r="AE112" t="n">
-        <v>100</v>
+        <v>139.34</v>
       </c>
       <c r="AF112" t="n">
-        <v>100</v>
+        <v>117.93</v>
       </c>
       <c r="AG112" t="n">
         <v>100</v>
@@ -14776,16 +14776,16 @@
         <v>139.34</v>
       </c>
       <c r="AN112" t="n">
-        <v>100</v>
+        <v>105.15</v>
       </c>
       <c r="AO112" t="n">
         <v>100</v>
       </c>
       <c r="AP112" t="n">
-        <v>105.15</v>
+        <v>136.05</v>
       </c>
       <c r="AQ112" t="n">
-        <v>105.15</v>
+        <v>139.34</v>
       </c>
       <c r="AR112" t="n">
         <v>100</v>
@@ -14858,22 +14858,22 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V113" t="n">
         <v>100</v>
@@ -16142,7 +16142,7 @@
         <v>249.25</v>
       </c>
       <c r="AX122" t="n">
-        <v>249.25</v>
+        <v>211.7</v>
       </c>
     </row>
     <row r="123">
@@ -16296,7 +16296,7 @@
         <v>249.25</v>
       </c>
       <c r="AX123" t="n">
-        <v>249.25</v>
+        <v>211.7</v>
       </c>
     </row>
     <row r="124">
@@ -16450,7 +16450,7 @@
         <v>249.25</v>
       </c>
       <c r="AX124" t="n">
-        <v>249.25</v>
+        <v>247.16</v>
       </c>
     </row>
     <row r="125">
@@ -17737,7 +17737,7 @@
         <v>30</v>
       </c>
       <c r="U135" t="n">
-        <v>30</v>
+        <v>34.21</v>
       </c>
       <c r="V135" t="n">
         <v>30</v>
@@ -17761,16 +17761,16 @@
         <v>30</v>
       </c>
       <c r="AC135" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AD135" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AE135" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AF135" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AG135" t="n">
         <v>30</v>
@@ -17788,28 +17788,28 @@
         <v>30</v>
       </c>
       <c r="AL135" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AM135" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AN135" t="n">
-        <v>30</v>
+        <v>32.84</v>
       </c>
       <c r="AO135" t="n">
         <v>30</v>
       </c>
       <c r="AP135" t="n">
-        <v>30</v>
+        <v>39.47</v>
       </c>
       <c r="AQ135" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AR135" t="n">
         <v>30</v>
       </c>
       <c r="AS135" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AT135" t="n">
         <v>30</v>
@@ -18764,7 +18764,7 @@
         <v>56.59</v>
       </c>
       <c r="AL144" t="n">
-        <v>56.59</v>
+        <v>57.11</v>
       </c>
       <c r="AM144" t="n">
         <v>56.59</v>
@@ -19328,10 +19328,10 @@
         <v>500</v>
       </c>
       <c r="T150" t="n">
-        <v>704</v>
+        <v>500</v>
       </c>
       <c r="U150" t="n">
-        <v>704</v>
+        <v>604.61</v>
       </c>
       <c r="V150" t="n">
         <v>704</v>
@@ -19355,19 +19355,19 @@
         <v>500</v>
       </c>
       <c r="AC150" t="n">
-        <v>500</v>
+        <v>712.73</v>
       </c>
       <c r="AD150" t="n">
-        <v>500</v>
+        <v>720.86</v>
       </c>
       <c r="AE150" t="n">
-        <v>500</v>
+        <v>766.37</v>
       </c>
       <c r="AF150" t="n">
-        <v>500</v>
+        <v>704</v>
       </c>
       <c r="AG150" t="n">
-        <v>500</v>
+        <v>704</v>
       </c>
       <c r="AH150" t="n">
         <v>500</v>
@@ -19382,37 +19382,37 @@
         <v>500</v>
       </c>
       <c r="AL150" t="n">
-        <v>841.79</v>
+        <v>862.4</v>
       </c>
       <c r="AM150" t="n">
+        <v>840.86</v>
+      </c>
+      <c r="AN150" t="n">
         <v>704</v>
-      </c>
-      <c r="AN150" t="n">
-        <v>639.02</v>
       </c>
       <c r="AO150" t="n">
         <v>704</v>
       </c>
       <c r="AP150" t="n">
-        <v>698.8099999999999</v>
+        <v>704</v>
       </c>
       <c r="AQ150" t="n">
         <v>704</v>
       </c>
       <c r="AR150" t="n">
-        <v>602.27</v>
+        <v>647.33</v>
       </c>
       <c r="AS150" t="n">
-        <v>837.08</v>
+        <v>704</v>
       </c>
       <c r="AT150" t="n">
-        <v>691.5</v>
+        <v>704</v>
       </c>
       <c r="AU150" t="n">
-        <v>675.67</v>
+        <v>704</v>
       </c>
       <c r="AV150" t="n">
-        <v>704</v>
+        <v>514.49</v>
       </c>
       <c r="AW150" t="n">
         <v>500</v>
@@ -19479,25 +19479,25 @@
         <v>500</v>
       </c>
       <c r="S151" t="n">
-        <v>506.06</v>
+        <v>500</v>
       </c>
       <c r="T151" t="n">
-        <v>684.86</v>
+        <v>568.34</v>
       </c>
       <c r="U151" t="n">
         <v>704</v>
       </c>
       <c r="V151" t="n">
-        <v>631.97</v>
+        <v>636.8200000000001</v>
       </c>
       <c r="W151" t="n">
-        <v>586.41</v>
+        <v>616.35</v>
       </c>
       <c r="X151" t="n">
-        <v>561.71</v>
+        <v>656.34</v>
       </c>
       <c r="Y151" t="n">
-        <v>500</v>
+        <v>690.26</v>
       </c>
       <c r="Z151" t="n">
         <v>500</v>
@@ -19509,22 +19509,22 @@
         <v>500</v>
       </c>
       <c r="AC151" t="n">
-        <v>598.65</v>
+        <v>704</v>
       </c>
       <c r="AD151" t="n">
-        <v>606.97</v>
+        <v>704</v>
       </c>
       <c r="AE151" t="n">
-        <v>630.02</v>
+        <v>704</v>
       </c>
       <c r="AF151" t="n">
-        <v>631.4400000000001</v>
+        <v>704</v>
       </c>
       <c r="AG151" t="n">
-        <v>557.36</v>
+        <v>665.8099999999999</v>
       </c>
       <c r="AH151" t="n">
-        <v>500</v>
+        <v>542.28</v>
       </c>
       <c r="AI151" t="n">
         <v>500</v>
@@ -19533,40 +19533,40 @@
         <v>500</v>
       </c>
       <c r="AK151" t="n">
-        <v>500</v>
+        <v>560.62</v>
       </c>
       <c r="AL151" t="n">
         <v>862.4</v>
       </c>
       <c r="AM151" t="n">
-        <v>859.12</v>
+        <v>862.4</v>
       </c>
       <c r="AN151" t="n">
         <v>704</v>
       </c>
       <c r="AO151" t="n">
-        <v>698.95</v>
+        <v>672.17</v>
       </c>
       <c r="AP151" t="n">
         <v>704</v>
       </c>
       <c r="AQ151" t="n">
-        <v>693.29</v>
+        <v>704</v>
       </c>
       <c r="AR151" t="n">
         <v>704</v>
       </c>
       <c r="AS151" t="n">
+        <v>781.1799999999999</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>594.86</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>654.47</v>
+      </c>
+      <c r="AV151" t="n">
         <v>704</v>
-      </c>
-      <c r="AT151" t="n">
-        <v>704</v>
-      </c>
-      <c r="AU151" t="n">
-        <v>500</v>
-      </c>
-      <c r="AV151" t="n">
-        <v>563.84</v>
       </c>
       <c r="AW151" t="n">
         <v>500</v>
@@ -19673,13 +19673,13 @@
         <v>901.6</v>
       </c>
       <c r="O153" t="n">
-        <v>901.6</v>
+        <v>783.73</v>
       </c>
       <c r="P153" t="n">
-        <v>747.03</v>
+        <v>600.4400000000001</v>
       </c>
       <c r="Q153" t="n">
-        <v>901.6</v>
+        <v>900.4400000000001</v>
       </c>
       <c r="R153" t="n">
         <v>901.6</v>
@@ -20347,112 +20347,112 @@
         <v>4968.66</v>
       </c>
       <c r="O160" t="n">
-        <v>4422.27</v>
+        <v>4204.4</v>
       </c>
       <c r="P160" t="n">
-        <v>4192.9</v>
+        <v>4177.32</v>
       </c>
       <c r="Q160" t="n">
-        <v>4716.24</v>
+        <v>4642.23</v>
       </c>
       <c r="R160" t="n">
-        <v>5135.22</v>
+        <v>5315.65</v>
       </c>
       <c r="S160" t="n">
-        <v>5863.33</v>
+        <v>5891.56</v>
       </c>
       <c r="T160" t="n">
-        <v>5919.94</v>
+        <v>5913.71</v>
       </c>
       <c r="U160" t="n">
-        <v>5975.89</v>
+        <v>6185.29</v>
       </c>
       <c r="V160" t="n">
-        <v>6008.33</v>
+        <v>6190.32</v>
       </c>
       <c r="W160" t="n">
-        <v>5959.56</v>
+        <v>6191.64</v>
       </c>
       <c r="X160" t="n">
-        <v>5939.59</v>
+        <v>6236.36</v>
       </c>
       <c r="Y160" t="n">
-        <v>5645.92</v>
+        <v>6068.32</v>
       </c>
       <c r="Z160" t="n">
-        <v>5385.89</v>
+        <v>5583.03</v>
       </c>
       <c r="AA160" t="n">
-        <v>5278.57</v>
+        <v>5575.71</v>
       </c>
       <c r="AB160" t="n">
-        <v>5531.1</v>
+        <v>5656.02</v>
       </c>
       <c r="AC160" t="n">
-        <v>6125.05</v>
+        <v>6534.95</v>
       </c>
       <c r="AD160" t="n">
-        <v>6174.41</v>
+        <v>6554.12</v>
       </c>
       <c r="AE160" t="n">
-        <v>6085.74</v>
+        <v>6527.91</v>
       </c>
       <c r="AF160" t="n">
-        <v>6058.99</v>
+        <v>6423.72</v>
       </c>
       <c r="AG160" t="n">
-        <v>6027.63</v>
+        <v>6390.08</v>
       </c>
       <c r="AH160" t="n">
-        <v>5880.03</v>
+        <v>6127.31</v>
       </c>
       <c r="AI160" t="n">
-        <v>5654.58</v>
+        <v>5748.61</v>
       </c>
       <c r="AJ160" t="n">
-        <v>5534.11</v>
+        <v>5529.36</v>
       </c>
       <c r="AK160" t="n">
-        <v>5986.83</v>
+        <v>6076.45</v>
       </c>
       <c r="AL160" t="n">
-        <v>6779.46</v>
+        <v>6810.59</v>
       </c>
       <c r="AM160" t="n">
-        <v>6638.39</v>
+        <v>6788.53</v>
       </c>
       <c r="AN160" t="n">
-        <v>6356.47</v>
+        <v>6432.38</v>
       </c>
       <c r="AO160" t="n">
-        <v>6413.4</v>
+        <v>6386.62</v>
       </c>
       <c r="AP160" t="n">
-        <v>6421.35</v>
+        <v>6484.57</v>
       </c>
       <c r="AQ160" t="n">
-        <v>6269.83</v>
+        <v>6344.27</v>
       </c>
       <c r="AR160" t="n">
-        <v>6129.72</v>
+        <v>6174.78</v>
       </c>
       <c r="AS160" t="n">
-        <v>6269.21</v>
+        <v>6223.31</v>
       </c>
       <c r="AT160" t="n">
-        <v>6031.66</v>
+        <v>5965.17</v>
       </c>
       <c r="AU160" t="n">
-        <v>5684.83</v>
+        <v>5781.83</v>
       </c>
       <c r="AV160" t="n">
-        <v>5267</v>
+        <v>5217.65</v>
       </c>
       <c r="AW160" t="n">
         <v>4876.91</v>
       </c>
       <c r="AX160" t="n">
-        <v>4486.91</v>
+        <v>4409.72</v>
       </c>
     </row>
     <row r="161">
@@ -20499,112 +20499,112 @@
         <v>6181.6</v>
       </c>
       <c r="O161" t="n">
-        <v>5996.68</v>
+        <v>6029.68</v>
       </c>
       <c r="P161" t="n">
-        <v>5973.37</v>
+        <v>6023.36</v>
       </c>
       <c r="Q161" t="n">
-        <v>6106.84</v>
+        <v>6157.95</v>
       </c>
       <c r="R161" t="n">
-        <v>6295.11</v>
+        <v>6347.8</v>
       </c>
       <c r="S161" t="n">
-        <v>6462.99</v>
+        <v>6517.08</v>
       </c>
       <c r="T161" t="n">
-        <v>6577.59</v>
+        <v>6632.63</v>
       </c>
       <c r="U161" t="n">
-        <v>6611.91</v>
+        <v>6667.24</v>
       </c>
       <c r="V161" t="n">
-        <v>6633</v>
+        <v>6688.5</v>
       </c>
       <c r="W161" t="n">
-        <v>6703.71</v>
+        <v>6759.81</v>
       </c>
       <c r="X161" t="n">
-        <v>6685.81</v>
+        <v>6741.75</v>
       </c>
       <c r="Y161" t="n">
-        <v>6621.73</v>
+        <v>6677.15</v>
       </c>
       <c r="Z161" t="n">
-        <v>6375.32</v>
+        <v>6428.67</v>
       </c>
       <c r="AA161" t="n">
-        <v>6374.61</v>
+        <v>6427.95</v>
       </c>
       <c r="AB161" t="n">
-        <v>6603.28</v>
+        <v>6658.54</v>
       </c>
       <c r="AC161" t="n">
-        <v>6888.75</v>
+        <v>6946.4</v>
       </c>
       <c r="AD161" t="n">
-        <v>6899.54</v>
+        <v>6957.28</v>
       </c>
       <c r="AE161" t="n">
-        <v>6940.8</v>
+        <v>6998.88</v>
       </c>
       <c r="AF161" t="n">
-        <v>6969.33</v>
+        <v>7027.65</v>
       </c>
       <c r="AG161" t="n">
-        <v>6993.67</v>
+        <v>7052.19</v>
       </c>
       <c r="AH161" t="n">
-        <v>6978.94</v>
+        <v>7037.34</v>
       </c>
       <c r="AI161" t="n">
-        <v>7003.75</v>
+        <v>7062.36</v>
       </c>
       <c r="AJ161" t="n">
-        <v>6973.63</v>
+        <v>7031.99</v>
       </c>
       <c r="AK161" t="n">
-        <v>7108.65</v>
+        <v>7168.14</v>
       </c>
       <c r="AL161" t="n">
-        <v>7394.2</v>
+        <v>7456.09</v>
       </c>
       <c r="AM161" t="n">
-        <v>7354.01</v>
+        <v>7415.56</v>
       </c>
       <c r="AN161" t="n">
-        <v>7281.97</v>
+        <v>7342.92</v>
       </c>
       <c r="AO161" t="n">
-        <v>7265.24</v>
+        <v>7326.05</v>
       </c>
       <c r="AP161" t="n">
-        <v>7217.75</v>
+        <v>7278.16</v>
       </c>
       <c r="AQ161" t="n">
-        <v>7187.09</v>
+        <v>7247.24</v>
       </c>
       <c r="AR161" t="n">
-        <v>7086.82</v>
+        <v>7146.13</v>
       </c>
       <c r="AS161" t="n">
-        <v>6945.49</v>
+        <v>7003.61</v>
       </c>
       <c r="AT161" t="n">
-        <v>6791.19</v>
+        <v>6848.02</v>
       </c>
       <c r="AU161" t="n">
-        <v>6691.02</v>
+        <v>6747.01</v>
       </c>
       <c r="AV161" t="n">
-        <v>6568.11</v>
+        <v>6623.08</v>
       </c>
       <c r="AW161" t="n">
-        <v>6467.5</v>
+        <v>6521.62</v>
       </c>
       <c r="AX161" t="n">
-        <v>6351.86</v>
+        <v>6405.01</v>
       </c>
     </row>
     <row r="162">
@@ -22181,112 +22181,112 @@
         <v>450</v>
       </c>
       <c r="O176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="P176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="Q176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="R176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="S176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="T176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="U176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="V176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="W176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="X176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="Y176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="Z176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AA176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AB176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AC176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AD176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AE176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AF176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AG176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AH176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AI176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AJ176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AK176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AL176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AM176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AN176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AO176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AP176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AQ176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AR176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AS176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AT176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AU176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AV176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AW176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="AX176" t="n">
-        <v>450</v>
+        <v>460</v>
       </c>
     </row>
     <row r="177">
@@ -22631,67 +22631,67 @@
         <v>250</v>
       </c>
       <c r="O179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="P179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Q179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="R179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="S179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="T179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="U179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="W179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="X179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Y179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Z179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AA179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AC179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AD179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AE179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AG179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AH179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AI179" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AJ179" t="n">
         <v>270</v>
@@ -22785,67 +22785,67 @@
         <v>250</v>
       </c>
       <c r="O180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="P180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Q180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="R180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="S180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="T180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="U180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="V180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="W180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="X180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Y180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="Z180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AA180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AC180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AD180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AE180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AG180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AH180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AI180" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AJ180" t="n">
         <v>270</v>
@@ -23441,16 +23441,16 @@
         <v>274.4</v>
       </c>
       <c r="O185" t="n">
-        <v>184.62</v>
+        <v>184.4</v>
       </c>
       <c r="P185" t="n">
-        <v>149.62</v>
+        <v>141</v>
       </c>
       <c r="Q185" t="n">
-        <v>239.62</v>
+        <v>219.11</v>
       </c>
       <c r="R185" t="n">
-        <v>274.4</v>
+        <v>233</v>
       </c>
       <c r="S185" t="n">
         <v>274.4</v>
@@ -23474,7 +23474,7 @@
         <v>274.4</v>
       </c>
       <c r="Z185" t="n">
-        <v>233</v>
+        <v>274.4</v>
       </c>
       <c r="AA185" t="n">
         <v>233</v>
@@ -23543,7 +23543,7 @@
         <v>274.4</v>
       </c>
       <c r="AW185" t="n">
-        <v>274.4</v>
+        <v>233</v>
       </c>
       <c r="AX185" t="n">
         <v>233</v>
@@ -23595,16 +23595,16 @@
         <v>274.4</v>
       </c>
       <c r="O186" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="P186" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>143</v>
+      </c>
+      <c r="R186" t="n">
         <v>233</v>
-      </c>
-      <c r="P186" t="n">
-        <v>143</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>233</v>
-      </c>
-      <c r="R186" t="n">
-        <v>274.4</v>
       </c>
       <c r="S186" t="n">
         <v>274.4</v>
@@ -23628,10 +23628,10 @@
         <v>274.4</v>
       </c>
       <c r="Z186" t="n">
-        <v>240.21</v>
+        <v>274.4</v>
       </c>
       <c r="AA186" t="n">
-        <v>233</v>
+        <v>271.21</v>
       </c>
       <c r="AB186" t="n">
         <v>274.4</v>
@@ -23697,7 +23697,7 @@
         <v>274.4</v>
       </c>
       <c r="AW186" t="n">
-        <v>274.4</v>
+        <v>264.3</v>
       </c>
       <c r="AX186" t="n">
         <v>233</v>
@@ -23906,7 +23906,7 @@
         <v>500</v>
       </c>
       <c r="P188" t="n">
-        <v>500</v>
+        <v>472.5</v>
       </c>
       <c r="Q188" t="n">
         <v>500</v>
@@ -25073,16 +25073,16 @@
         <v>375</v>
       </c>
       <c r="O197" t="n">
-        <v>375</v>
+        <v>555</v>
       </c>
       <c r="P197" t="n">
-        <v>465</v>
+        <v>604.88</v>
       </c>
       <c r="Q197" t="n">
-        <v>555</v>
+        <v>604.88</v>
       </c>
       <c r="R197" t="n">
-        <v>645</v>
+        <v>604.88</v>
       </c>
       <c r="S197" t="n">
         <v>647.58</v>
@@ -25133,10 +25133,10 @@
         <v>647.58</v>
       </c>
       <c r="AI197" t="n">
-        <v>604.88</v>
+        <v>647.58</v>
       </c>
       <c r="AJ197" t="n">
-        <v>604.88</v>
+        <v>647.58</v>
       </c>
       <c r="AK197" t="n">
         <v>647.58</v>
@@ -25178,7 +25178,7 @@
         <v>647.58</v>
       </c>
       <c r="AX197" t="n">
-        <v>647.58</v>
+        <v>604.88</v>
       </c>
     </row>
     <row r="198">
@@ -25233,10 +25233,10 @@
         <v>604.88</v>
       </c>
       <c r="Q198" t="n">
-        <v>647.58</v>
+        <v>604.88</v>
       </c>
       <c r="R198" t="n">
-        <v>647.58</v>
+        <v>604.88</v>
       </c>
       <c r="S198" t="n">
         <v>647.58</v>
@@ -25287,10 +25287,10 @@
         <v>647.58</v>
       </c>
       <c r="AI198" t="n">
-        <v>626.77</v>
+        <v>647.58</v>
       </c>
       <c r="AJ198" t="n">
-        <v>604.88</v>
+        <v>647.58</v>
       </c>
       <c r="AK198" t="n">
         <v>647.58</v>
@@ -25332,7 +25332,7 @@
         <v>647.58</v>
       </c>
       <c r="AX198" t="n">
-        <v>612.9</v>
+        <v>604.88</v>
       </c>
     </row>
     <row r="199">
@@ -25598,7 +25598,7 @@
         <v>647.88</v>
       </c>
       <c r="AJ200" t="n">
-        <v>637.83</v>
+        <v>647.88</v>
       </c>
       <c r="AK200" t="n">
         <v>647.88</v>
@@ -25739,112 +25739,112 @@
         <v>8357.200000000001</v>
       </c>
       <c r="O202" t="n">
-        <v>8183.32</v>
+        <v>8304.5</v>
       </c>
       <c r="P202" t="n">
-        <v>8249.940000000001</v>
+        <v>8341.700000000001</v>
       </c>
       <c r="Q202" t="n">
-        <v>8562.639999999999</v>
+        <v>8449.309999999999</v>
       </c>
       <c r="R202" t="n">
-        <v>8830.43</v>
+        <v>8654.809999999999</v>
       </c>
       <c r="S202" t="n">
-        <v>8827.01</v>
+        <v>8817.01</v>
       </c>
       <c r="T202" t="n">
-        <v>8885.08</v>
+        <v>8875.08</v>
       </c>
       <c r="U202" t="n">
-        <v>8885.08</v>
+        <v>8875.08</v>
       </c>
       <c r="V202" t="n">
-        <v>8986.690000000001</v>
+        <v>8976.690000000001</v>
       </c>
       <c r="W202" t="n">
-        <v>9001.209999999999</v>
+        <v>8991.209999999999</v>
       </c>
       <c r="X202" t="n">
-        <v>9001.209999999999</v>
+        <v>8991.209999999999</v>
       </c>
       <c r="Y202" t="n">
-        <v>9001.209999999999</v>
+        <v>8991.209999999999</v>
       </c>
       <c r="Z202" t="n">
-        <v>8853.040000000001</v>
+        <v>8918.629999999999</v>
       </c>
       <c r="AA202" t="n">
-        <v>8845.83</v>
+        <v>8874.040000000001</v>
       </c>
       <c r="AB202" t="n">
-        <v>9103.209999999999</v>
+        <v>9093.209999999999</v>
       </c>
       <c r="AC202" t="n">
-        <v>9103.370000000001</v>
+        <v>9093.370000000001</v>
       </c>
       <c r="AD202" t="n">
-        <v>9103.370000000001</v>
+        <v>9093.370000000001</v>
       </c>
       <c r="AE202" t="n">
-        <v>9103.370000000001</v>
+        <v>9093.370000000001</v>
       </c>
       <c r="AF202" t="n">
-        <v>9103.370000000001</v>
+        <v>9093.370000000001</v>
       </c>
       <c r="AG202" t="n">
-        <v>9103.370000000001</v>
+        <v>9093.370000000001</v>
       </c>
       <c r="AH202" t="n">
-        <v>8941.790000000001</v>
+        <v>8931.790000000001</v>
       </c>
       <c r="AI202" t="n">
-        <v>8878.280000000001</v>
+        <v>8931.790000000001</v>
       </c>
       <c r="AJ202" t="n">
-        <v>8886.34</v>
+        <v>8991.790000000001</v>
       </c>
       <c r="AK202" t="n">
-        <v>8981.790000000001</v>
+        <v>8991.790000000001</v>
       </c>
       <c r="AL202" t="n">
-        <v>9000.66</v>
+        <v>9010.66</v>
       </c>
       <c r="AM202" t="n">
-        <v>8981.790000000001</v>
+        <v>8991.790000000001</v>
       </c>
       <c r="AN202" t="n">
-        <v>8981.790000000001</v>
+        <v>8991.790000000001</v>
       </c>
       <c r="AO202" t="n">
-        <v>8981.790000000001</v>
+        <v>8991.790000000001</v>
       </c>
       <c r="AP202" t="n">
-        <v>8841.790000000001</v>
+        <v>8851.790000000001</v>
       </c>
       <c r="AQ202" t="n">
-        <v>8841.790000000001</v>
+        <v>8851.790000000001</v>
       </c>
       <c r="AR202" t="n">
-        <v>8841.790000000001</v>
+        <v>8851.790000000001</v>
       </c>
       <c r="AS202" t="n">
-        <v>8727.18</v>
+        <v>8737.18</v>
       </c>
       <c r="AT202" t="n">
-        <v>8625.559999999999</v>
+        <v>8635.559999999999</v>
       </c>
       <c r="AU202" t="n">
-        <v>8523.940000000001</v>
+        <v>8533.940000000001</v>
       </c>
       <c r="AV202" t="n">
-        <v>8523.940000000001</v>
+        <v>8533.940000000001</v>
       </c>
       <c r="AW202" t="n">
-        <v>8523.940000000001</v>
+        <v>8482.440000000001</v>
       </c>
       <c r="AX202" t="n">
-        <v>8406.459999999999</v>
+        <v>8365.74</v>
       </c>
     </row>
     <row r="203">
@@ -25891,112 +25891,112 @@
         <v>4568.44</v>
       </c>
       <c r="O203" t="n">
-        <v>4412.13</v>
+        <v>4437.02</v>
       </c>
       <c r="P203" t="n">
-        <v>4350.3</v>
+        <v>4387.3</v>
       </c>
       <c r="Q203" t="n">
-        <v>4571.54</v>
+        <v>4610.42</v>
       </c>
       <c r="R203" t="n">
-        <v>4727.28</v>
+        <v>4767.49</v>
       </c>
       <c r="S203" t="n">
-        <v>4926.72</v>
+        <v>4968.62</v>
       </c>
       <c r="T203" t="n">
-        <v>5026.58</v>
+        <v>5069.34</v>
       </c>
       <c r="U203" t="n">
-        <v>5096.16</v>
+        <v>5139.51</v>
       </c>
       <c r="V203" t="n">
-        <v>5141.37</v>
+        <v>5185.1</v>
       </c>
       <c r="W203" t="n">
-        <v>5184.85</v>
+        <v>5228.95</v>
       </c>
       <c r="X203" t="n">
-        <v>5202.56</v>
+        <v>5246.81</v>
       </c>
       <c r="Y203" t="n">
-        <v>5143.69</v>
+        <v>5187.44</v>
       </c>
       <c r="Z203" t="n">
-        <v>4983.13</v>
+        <v>5025.51</v>
       </c>
       <c r="AA203" t="n">
-        <v>4981.56</v>
+        <v>5023.93</v>
       </c>
       <c r="AB203" t="n">
-        <v>5148.98</v>
+        <v>5192.78</v>
       </c>
       <c r="AC203" t="n">
-        <v>5373.78</v>
+        <v>5419.49</v>
       </c>
       <c r="AD203" t="n">
-        <v>5358.72</v>
+        <v>5404.3</v>
       </c>
       <c r="AE203" t="n">
-        <v>5358</v>
+        <v>5403.57</v>
       </c>
       <c r="AF203" t="n">
-        <v>5343.73</v>
+        <v>5389.18</v>
       </c>
       <c r="AG203" t="n">
-        <v>5320.32</v>
+        <v>5365.58</v>
       </c>
       <c r="AH203" t="n">
-        <v>5223.61</v>
+        <v>5268.04</v>
       </c>
       <c r="AI203" t="n">
-        <v>5184.24</v>
+        <v>5228.33</v>
       </c>
       <c r="AJ203" t="n">
-        <v>5175.5</v>
+        <v>5219.52</v>
       </c>
       <c r="AK203" t="n">
-        <v>5388.54</v>
+        <v>5434.38</v>
       </c>
       <c r="AL203" t="n">
-        <v>5826.8</v>
+        <v>5876.36</v>
       </c>
       <c r="AM203" t="n">
-        <v>5802.23</v>
+        <v>5851.58</v>
       </c>
       <c r="AN203" t="n">
-        <v>5744.14</v>
+        <v>5793</v>
       </c>
       <c r="AO203" t="n">
-        <v>5656.62</v>
+        <v>5704.73</v>
       </c>
       <c r="AP203" t="n">
-        <v>5609.17</v>
+        <v>5656.88</v>
       </c>
       <c r="AQ203" t="n">
-        <v>5499.46</v>
+        <v>5546.23</v>
       </c>
       <c r="AR203" t="n">
-        <v>5365.68</v>
+        <v>5411.32</v>
       </c>
       <c r="AS203" t="n">
-        <v>5170.83</v>
+        <v>5214.81</v>
       </c>
       <c r="AT203" t="n">
-        <v>4996.5</v>
+        <v>5038.99</v>
       </c>
       <c r="AU203" t="n">
-        <v>4832.22</v>
+        <v>4873.32</v>
       </c>
       <c r="AV203" t="n">
-        <v>4680.24</v>
+        <v>4720.05</v>
       </c>
       <c r="AW203" t="n">
-        <v>4593.17</v>
+        <v>4632.24</v>
       </c>
       <c r="AX203" t="n">
-        <v>4499.2</v>
+        <v>4537.47</v>
       </c>
     </row>
     <row r="204">
@@ -26602,28 +26602,28 @@
         <v>154.95</v>
       </c>
       <c r="P209" t="n">
-        <v>154.95</v>
+        <v>174.12</v>
       </c>
       <c r="Q209" t="n">
-        <v>174.12</v>
+        <v>240.18</v>
       </c>
       <c r="R209" t="n">
-        <v>253.58</v>
+        <v>264.78</v>
       </c>
       <c r="S209" t="n">
-        <v>253.91</v>
+        <v>265.11</v>
       </c>
       <c r="T209" t="n">
-        <v>259.04</v>
+        <v>270.55</v>
       </c>
       <c r="U209" t="n">
-        <v>258.91</v>
+        <v>270.49</v>
       </c>
       <c r="V209" t="n">
-        <v>277.97</v>
+        <v>289.61</v>
       </c>
       <c r="W209" t="n">
-        <v>325.4</v>
+        <v>329.24</v>
       </c>
       <c r="X209" t="n">
         <v>325.4</v>
@@ -26641,55 +26641,55 @@
         <v>325.4</v>
       </c>
       <c r="AC209" t="n">
-        <v>342.7</v>
+        <v>354.66</v>
       </c>
       <c r="AD209" t="n">
-        <v>358.95</v>
+        <v>371.04</v>
       </c>
       <c r="AE209" t="n">
-        <v>379.99</v>
+        <v>392.26</v>
       </c>
       <c r="AF209" t="n">
-        <v>372.94</v>
+        <v>385.15</v>
       </c>
       <c r="AG209" t="n">
-        <v>378.97</v>
+        <v>391.23</v>
       </c>
       <c r="AH209" t="n">
-        <v>355.65</v>
+        <v>367.72</v>
       </c>
       <c r="AI209" t="n">
-        <v>345.85</v>
+        <v>357.83</v>
       </c>
       <c r="AJ209" t="n">
-        <v>353.67</v>
+        <v>365.75</v>
       </c>
       <c r="AK209" t="n">
-        <v>433.85</v>
+        <v>446.61</v>
       </c>
       <c r="AL209" t="n">
-        <v>441.32</v>
+        <v>454.29</v>
       </c>
       <c r="AM209" t="n">
-        <v>437.45</v>
+        <v>450.25</v>
       </c>
       <c r="AN209" t="n">
-        <v>414.79</v>
+        <v>427.41</v>
       </c>
       <c r="AO209" t="n">
-        <v>422.49</v>
+        <v>435.15</v>
       </c>
       <c r="AP209" t="n">
-        <v>392.53</v>
+        <v>404.94</v>
       </c>
       <c r="AQ209" t="n">
-        <v>320.32</v>
+        <v>332.53</v>
       </c>
       <c r="AR209" t="n">
-        <v>288.23</v>
+        <v>300.18</v>
       </c>
       <c r="AS209" t="n">
-        <v>244.79</v>
+        <v>256.29</v>
       </c>
       <c r="AT209" t="n">
         <v>154.95</v>
@@ -28429,43 +28429,43 @@
         <v>330</v>
       </c>
       <c r="O223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="P223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="Q223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="R223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="S223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="T223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="U223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="V223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="W223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="X223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="Y223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="Z223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AA223" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AB223" t="n">
         <v>340</v>
@@ -28583,43 +28583,43 @@
         <v>330</v>
       </c>
       <c r="O224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="P224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="Q224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="R224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="S224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="T224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="U224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="V224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="W224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="X224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="Y224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="Z224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AA224" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AB224" t="n">
         <v>340</v>
@@ -29147,16 +29147,16 @@
         <v>242.25</v>
       </c>
       <c r="O229" t="n">
-        <v>242.25</v>
+        <v>254.99</v>
       </c>
       <c r="P229" t="n">
-        <v>242.25</v>
+        <v>280.47</v>
       </c>
       <c r="Q229" t="n">
-        <v>254.99</v>
+        <v>326.17</v>
       </c>
       <c r="R229" t="n">
-        <v>280.47</v>
+        <v>326.17</v>
       </c>
       <c r="S229" t="n">
         <v>326.17</v>
@@ -29335,58 +29335,58 @@
         <v>155</v>
       </c>
       <c r="AA230" t="n">
+        <v>155</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>155</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>155</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>155</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>155</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>155</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>155</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>155</v>
+      </c>
+      <c r="AI230" t="n">
         <v>220.25</v>
       </c>
-      <c r="AB230" t="n">
-        <v>310</v>
-      </c>
-      <c r="AC230" t="n">
-        <v>310</v>
-      </c>
-      <c r="AD230" t="n">
-        <v>310</v>
-      </c>
-      <c r="AE230" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF230" t="n">
-        <v>310</v>
-      </c>
-      <c r="AG230" t="n">
-        <v>310</v>
-      </c>
-      <c r="AH230" t="n">
-        <v>310</v>
-      </c>
-      <c r="AI230" t="n">
-        <v>375.25</v>
-      </c>
       <c r="AJ230" t="n">
-        <v>392.15</v>
+        <v>237.15</v>
       </c>
       <c r="AK230" t="n">
-        <v>392.15</v>
+        <v>237.15</v>
       </c>
       <c r="AL230" t="n">
-        <v>392.15</v>
+        <v>237.15</v>
       </c>
       <c r="AM230" t="n">
-        <v>392.15</v>
+        <v>237.15</v>
       </c>
       <c r="AN230" t="n">
-        <v>392.15</v>
+        <v>237.15</v>
       </c>
       <c r="AO230" t="n">
-        <v>392.15</v>
+        <v>237.15</v>
       </c>
       <c r="AP230" t="n">
-        <v>392.15</v>
+        <v>237.15</v>
       </c>
       <c r="AQ230" t="n">
-        <v>392.15</v>
+        <v>237.15</v>
       </c>
       <c r="AR230" t="n">
-        <v>269.69</v>
+        <v>155</v>
       </c>
       <c r="AS230" t="n">
         <v>155</v>
@@ -29759,7 +29759,7 @@
         <v>323</v>
       </c>
       <c r="AW233" t="n">
-        <v>323</v>
+        <v>322.75</v>
       </c>
       <c r="AX233" t="n">
         <v>322.75</v>
@@ -31382,46 +31382,46 @@
         <v>0</v>
       </c>
       <c r="V248" t="n">
+        <v>0</v>
+      </c>
+      <c r="W248" t="n">
+        <v>0</v>
+      </c>
+      <c r="X248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z248" t="n">
         <v>40.75</v>
       </c>
-      <c r="W248" t="n">
+      <c r="AA248" t="n">
         <v>122.25</v>
       </c>
-      <c r="X248" t="n">
+      <c r="AB248" t="n">
         <v>203.75</v>
       </c>
-      <c r="Y248" t="n">
+      <c r="AC248" t="n">
         <v>285.25</v>
       </c>
-      <c r="Z248" t="n">
+      <c r="AD248" t="n">
         <v>366.75</v>
       </c>
-      <c r="AA248" t="n">
+      <c r="AE248" t="n">
         <v>448.25</v>
       </c>
-      <c r="AB248" t="n">
+      <c r="AF248" t="n">
         <v>529.75</v>
       </c>
-      <c r="AC248" t="n">
+      <c r="AG248" t="n">
         <v>611.25</v>
       </c>
-      <c r="AD248" t="n">
+      <c r="AH248" t="n">
         <v>692.75</v>
       </c>
-      <c r="AE248" t="n">
+      <c r="AI248" t="n">
         <v>771.74</v>
-      </c>
-      <c r="AF248" t="n">
-        <v>794.78</v>
-      </c>
-      <c r="AG248" t="n">
-        <v>794.78</v>
-      </c>
-      <c r="AH248" t="n">
-        <v>794.78</v>
-      </c>
-      <c r="AI248" t="n">
-        <v>794.78</v>
       </c>
       <c r="AJ248" t="n">
         <v>794.78</v>
@@ -32131,97 +32131,97 @@
         <v>4548.28</v>
       </c>
       <c r="O255" t="n">
-        <v>4537.28</v>
+        <v>4510.02</v>
       </c>
       <c r="P255" t="n">
-        <v>4615.61</v>
+        <v>4633</v>
       </c>
       <c r="Q255" t="n">
-        <v>4668.52</v>
+        <v>4765.76</v>
       </c>
       <c r="R255" t="n">
-        <v>4773.46</v>
+        <v>4790.36</v>
       </c>
       <c r="S255" t="n">
-        <v>4827.49</v>
+        <v>4798.69</v>
       </c>
       <c r="T255" t="n">
-        <v>4832.62</v>
+        <v>4804.13</v>
       </c>
       <c r="U255" t="n">
-        <v>4832.49</v>
+        <v>4804.07</v>
       </c>
       <c r="V255" t="n">
-        <v>4903.3</v>
+        <v>4834.19</v>
       </c>
       <c r="W255" t="n">
-        <v>5032.23</v>
+        <v>4873.82</v>
       </c>
       <c r="X255" t="n">
-        <v>5113.73</v>
+        <v>4869.98</v>
       </c>
       <c r="Y255" t="n">
-        <v>5194.23</v>
+        <v>4868.98</v>
       </c>
       <c r="Z255" t="n">
-        <v>5275.73</v>
+        <v>4909.73</v>
       </c>
       <c r="AA255" t="n">
-        <v>5431.86</v>
+        <v>5000.61</v>
       </c>
       <c r="AB255" t="n">
-        <v>5642.63</v>
+        <v>5161.63</v>
       </c>
       <c r="AC255" t="n">
-        <v>5769.23</v>
+        <v>5300.19</v>
       </c>
       <c r="AD255" t="n">
-        <v>5866.98</v>
+        <v>5398.07</v>
       </c>
       <c r="AE255" t="n">
-        <v>5956.01</v>
+        <v>5489.79</v>
       </c>
       <c r="AF255" t="n">
-        <v>5972</v>
+        <v>5564.18</v>
       </c>
       <c r="AG255" t="n">
-        <v>5978.03</v>
+        <v>5651.76</v>
       </c>
       <c r="AH255" t="n">
-        <v>5954.71</v>
+        <v>5709.75</v>
       </c>
       <c r="AI255" t="n">
-        <v>6010.16</v>
+        <v>5844.1</v>
       </c>
       <c r="AJ255" t="n">
-        <v>6038.88</v>
+        <v>5895.96</v>
       </c>
       <c r="AK255" t="n">
-        <v>6201.06</v>
+        <v>6058.82</v>
       </c>
       <c r="AL255" t="n">
-        <v>6209.53</v>
+        <v>6067.5</v>
       </c>
       <c r="AM255" t="n">
-        <v>6204.66</v>
+        <v>6062.46</v>
       </c>
       <c r="AN255" t="n">
-        <v>6248</v>
+        <v>6105.62</v>
       </c>
       <c r="AO255" t="n">
-        <v>6253.7</v>
+        <v>6111.36</v>
       </c>
       <c r="AP255" t="n">
-        <v>5992.74</v>
+        <v>5850.15</v>
       </c>
       <c r="AQ255" t="n">
-        <v>5922.53</v>
+        <v>5779.74</v>
       </c>
       <c r="AR255" t="n">
-        <v>5738.5</v>
+        <v>5635.76</v>
       </c>
       <c r="AS255" t="n">
-        <v>5436.52</v>
+        <v>5448.02</v>
       </c>
       <c r="AT255" t="n">
         <v>5295.49</v>
@@ -32233,7 +32233,7 @@
         <v>5261.76</v>
       </c>
       <c r="AW255" t="n">
-        <v>5261.76</v>
+        <v>5261.51</v>
       </c>
       <c r="AX255" t="n">
         <v>5262.51</v>
@@ -32283,112 +32283,112 @@
         <v>5804.2</v>
       </c>
       <c r="O256" t="n">
-        <v>5702.24</v>
+        <v>5734.4</v>
       </c>
       <c r="P256" t="n">
-        <v>5709.13</v>
+        <v>5757.69</v>
       </c>
       <c r="Q256" t="n">
-        <v>5940.77</v>
+        <v>5991.3</v>
       </c>
       <c r="R256" t="n">
-        <v>6236.51</v>
+        <v>6289.56</v>
       </c>
       <c r="S256" t="n">
-        <v>6393.59</v>
+        <v>6447.98</v>
       </c>
       <c r="T256" t="n">
-        <v>6474.05</v>
+        <v>6529.12</v>
       </c>
       <c r="U256" t="n">
-        <v>6500.57</v>
+        <v>6555.86</v>
       </c>
       <c r="V256" t="n">
-        <v>6582.49</v>
+        <v>6638.48</v>
       </c>
       <c r="W256" t="n">
-        <v>6587.69</v>
+        <v>6643.73</v>
       </c>
       <c r="X256" t="n">
-        <v>6593.82</v>
+        <v>6649.9</v>
       </c>
       <c r="Y256" t="n">
-        <v>6500.75</v>
+        <v>6556.05</v>
       </c>
       <c r="Z256" t="n">
-        <v>6300.69</v>
+        <v>6354.28</v>
       </c>
       <c r="AA256" t="n">
-        <v>6273.95</v>
+        <v>6327.31</v>
       </c>
       <c r="AB256" t="n">
-        <v>6452.01</v>
+        <v>6506.89</v>
       </c>
       <c r="AC256" t="n">
-        <v>6675.03</v>
+        <v>6731.8</v>
       </c>
       <c r="AD256" t="n">
-        <v>6756.75</v>
+        <v>6814.22</v>
       </c>
       <c r="AE256" t="n">
-        <v>6778.48</v>
+        <v>6836.14</v>
       </c>
       <c r="AF256" t="n">
-        <v>6779.06</v>
+        <v>6836.72</v>
       </c>
       <c r="AG256" t="n">
-        <v>6732.27</v>
+        <v>6789.53</v>
       </c>
       <c r="AH256" t="n">
-        <v>6617.83</v>
+        <v>6674.12</v>
       </c>
       <c r="AI256" t="n">
-        <v>6488.35</v>
+        <v>6543.54</v>
       </c>
       <c r="AJ256" t="n">
-        <v>6552.52</v>
+        <v>6608.26</v>
       </c>
       <c r="AK256" t="n">
-        <v>7000.12</v>
+        <v>7059.66</v>
       </c>
       <c r="AL256" t="n">
-        <v>7109.29</v>
+        <v>7169.76</v>
       </c>
       <c r="AM256" t="n">
-        <v>6975.15</v>
+        <v>7034.48</v>
       </c>
       <c r="AN256" t="n">
-        <v>6846.74</v>
+        <v>6904.98</v>
       </c>
       <c r="AO256" t="n">
-        <v>6845.74</v>
+        <v>6903.97</v>
       </c>
       <c r="AP256" t="n">
-        <v>6761.92</v>
+        <v>6819.43</v>
       </c>
       <c r="AQ256" t="n">
-        <v>6634.53</v>
+        <v>6690.96</v>
       </c>
       <c r="AR256" t="n">
-        <v>6544.6</v>
+        <v>6600.27</v>
       </c>
       <c r="AS256" t="n">
-        <v>6404.03</v>
+        <v>6458.5</v>
       </c>
       <c r="AT256" t="n">
-        <v>6251.6</v>
+        <v>6304.77</v>
       </c>
       <c r="AU256" t="n">
-        <v>6170.32</v>
+        <v>6222.8</v>
       </c>
       <c r="AV256" t="n">
-        <v>6010.77</v>
+        <v>6061.9</v>
       </c>
       <c r="AW256" t="n">
-        <v>5932.95</v>
+        <v>5983.42</v>
       </c>
       <c r="AX256" t="n">
-        <v>5843.74</v>
+        <v>5893.45</v>
       </c>
     </row>
     <row r="257">
@@ -33055,55 +33055,55 @@
         <v>85</v>
       </c>
       <c r="S263" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="T263" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="U263" t="n">
         <v>85</v>
       </c>
-      <c r="T263" t="n">
+      <c r="V263" t="n">
         <v>85</v>
       </c>
-      <c r="U263" t="n">
-        <v>92.55</v>
-      </c>
-      <c r="V263" t="n">
-        <v>85.81999999999999</v>
-      </c>
       <c r="W263" t="n">
+        <v>90.18000000000001</v>
+      </c>
+      <c r="X263" t="n">
         <v>85</v>
       </c>
-      <c r="X263" t="n">
-        <v>89.05</v>
-      </c>
       <c r="Y263" t="n">
-        <v>92.05</v>
+        <v>85</v>
       </c>
       <c r="Z263" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>93.97</v>
+      </c>
+      <c r="AB263" t="n">
         <v>85</v>
       </c>
-      <c r="AA263" t="n">
+      <c r="AC263" t="n">
+        <v>87.63</v>
+      </c>
+      <c r="AD263" t="n">
         <v>85</v>
-      </c>
-      <c r="AB263" t="n">
-        <v>89.84999999999999</v>
-      </c>
-      <c r="AC263" t="n">
-        <v>85</v>
-      </c>
-      <c r="AD263" t="n">
-        <v>88.08</v>
       </c>
       <c r="AE263" t="n">
         <v>85</v>
       </c>
       <c r="AF263" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AG263" t="n">
-        <v>85</v>
+        <v>92.88</v>
       </c>
       <c r="AH263" t="n">
-        <v>85</v>
+        <v>91.37</v>
       </c>
       <c r="AI263" t="n">
-        <v>85</v>
+        <v>87.79000000000001</v>
       </c>
       <c r="AJ263" t="n">
         <v>85</v>
@@ -33115,40 +33115,40 @@
         <v>85</v>
       </c>
       <c r="AM263" t="n">
-        <v>94</v>
+        <v>115.5</v>
       </c>
       <c r="AN263" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="AO263" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AP263" t="n">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="AQ263" t="n">
         <v>85</v>
       </c>
       <c r="AR263" t="n">
-        <v>114.67</v>
+        <v>129.67</v>
       </c>
       <c r="AS263" t="n">
-        <v>85</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="AT263" t="n">
         <v>85</v>
       </c>
       <c r="AU263" t="n">
-        <v>96.44</v>
+        <v>85</v>
       </c>
       <c r="AV263" t="n">
-        <v>89.47</v>
+        <v>85</v>
       </c>
       <c r="AW263" t="n">
-        <v>87.17</v>
+        <v>85</v>
       </c>
       <c r="AX263" t="n">
-        <v>92.53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="264">
@@ -33258,7 +33258,7 @@
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="S265" t="n">
         <v>40</v>
@@ -33315,25 +33315,25 @@
         <v>30</v>
       </c>
       <c r="AK265" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL265" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM265" t="n">
-        <v>36.3</v>
+        <v>30</v>
       </c>
       <c r="AN265" t="n">
         <v>40</v>
       </c>
       <c r="AO265" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP265" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AQ265" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AR265" t="n">
         <v>30</v>
@@ -33469,25 +33469,25 @@
         <v>30</v>
       </c>
       <c r="AK266" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="AL266" t="n">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="AM266" t="n">
         <v>30</v>
       </c>
       <c r="AN266" t="n">
-        <v>40</v>
+        <v>36.12</v>
       </c>
       <c r="AO266" t="n">
-        <v>39.44</v>
+        <v>36</v>
       </c>
       <c r="AP266" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AQ266" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="AR266" t="n">
         <v>30</v>
@@ -34244,40 +34244,40 @@
         <v>10</v>
       </c>
       <c r="T274" t="n">
-        <v>42.52</v>
+        <v>45.6</v>
       </c>
       <c r="U274" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="V274" t="n">
+        <v>45</v>
+      </c>
+      <c r="W274" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="X274" t="n">
         <v>10</v>
-      </c>
-      <c r="V274" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="W274" t="n">
-        <v>10</v>
-      </c>
-      <c r="X274" t="n">
-        <v>45.6</v>
       </c>
       <c r="Y274" t="n">
         <v>10</v>
       </c>
       <c r="Z274" t="n">
-        <v>41.35</v>
+        <v>45.6</v>
       </c>
       <c r="AA274" t="n">
-        <v>39.57</v>
+        <v>45.6</v>
       </c>
       <c r="AB274" t="n">
+        <v>45</v>
+      </c>
+      <c r="AC274" t="n">
         <v>45.6</v>
       </c>
-      <c r="AC274" t="n">
+      <c r="AD274" t="n">
         <v>10</v>
       </c>
-      <c r="AD274" t="n">
-        <v>45.6</v>
-      </c>
       <c r="AE274" t="n">
-        <v>23.99</v>
+        <v>10</v>
       </c>
       <c r="AF274" t="n">
         <v>10</v>
@@ -34292,49 +34292,49 @@
         <v>10</v>
       </c>
       <c r="AJ274" t="n">
-        <v>25.13</v>
+        <v>10</v>
       </c>
       <c r="AK274" t="n">
         <v>10</v>
       </c>
       <c r="AL274" t="n">
-        <v>10</v>
+        <v>45.6</v>
       </c>
       <c r="AM274" t="n">
         <v>45</v>
       </c>
       <c r="AN274" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="AO274" t="n">
-        <v>39.4</v>
+        <v>45</v>
       </c>
       <c r="AP274" t="n">
-        <v>39.4</v>
+        <v>45</v>
       </c>
       <c r="AQ274" t="n">
-        <v>39.4</v>
+        <v>45</v>
       </c>
       <c r="AR274" t="n">
         <v>45</v>
       </c>
       <c r="AS274" t="n">
-        <v>33.14</v>
+        <v>45</v>
       </c>
       <c r="AT274" t="n">
         <v>10</v>
       </c>
       <c r="AU274" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="AV274" t="n">
-        <v>45.6</v>
+        <v>10</v>
       </c>
       <c r="AW274" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="AX274" t="n">
-        <v>10</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="275">
@@ -34460,10 +34460,10 @@
         <v>10</v>
       </c>
       <c r="X276" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="Y276" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="Z276" t="n">
         <v>10</v>
@@ -34478,22 +34478,22 @@
         <v>10</v>
       </c>
       <c r="AD276" t="n">
-        <v>10</v>
+        <v>29.28</v>
       </c>
       <c r="AE276" t="n">
         <v>45</v>
       </c>
       <c r="AF276" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AG276" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AH276" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AI276" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AJ276" t="n">
         <v>45</v>
@@ -34508,7 +34508,7 @@
         <v>45</v>
       </c>
       <c r="AN276" t="n">
-        <v>45.6</v>
+        <v>39.4</v>
       </c>
       <c r="AO276" t="n">
         <v>45</v>
@@ -34526,13 +34526,13 @@
         <v>45</v>
       </c>
       <c r="AT276" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AU276" t="n">
         <v>10</v>
       </c>
       <c r="AV276" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="AW276" t="n">
         <v>10</v>
@@ -34658,16 +34658,16 @@
         <v>10</v>
       </c>
       <c r="V278" t="n">
-        <v>10</v>
+        <v>26.42</v>
       </c>
       <c r="W278" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="X278" t="n">
         <v>45</v>
       </c>
-      <c r="X278" t="n">
-        <v>45.6</v>
-      </c>
       <c r="Y278" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="Z278" t="n">
         <v>10</v>
@@ -34676,55 +34676,55 @@
         <v>10</v>
       </c>
       <c r="AB278" t="n">
-        <v>10</v>
+        <v>30.45</v>
       </c>
       <c r="AC278" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AD278" t="n">
         <v>45</v>
-      </c>
-      <c r="AD278" t="n">
-        <v>45.6</v>
       </c>
       <c r="AE278" t="n">
         <v>45</v>
       </c>
       <c r="AF278" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AG278" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AH278" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AI278" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AJ278" t="n">
-        <v>45</v>
+        <v>40.13</v>
       </c>
       <c r="AK278" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AL278" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="AM278" t="n">
         <v>39.4</v>
       </c>
       <c r="AN278" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="AO278" t="n">
         <v>45</v>
       </c>
       <c r="AP278" t="n">
-        <v>45</v>
+        <v>39.4</v>
       </c>
       <c r="AQ278" t="n">
-        <v>45</v>
+        <v>42.55</v>
       </c>
       <c r="AR278" t="n">
-        <v>45</v>
+        <v>39.4</v>
       </c>
       <c r="AS278" t="n">
         <v>45</v>
@@ -34736,10 +34736,10 @@
         <v>10</v>
       </c>
       <c r="AV278" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="AW278" t="n">
-        <v>10</v>
+        <v>27.77</v>
       </c>
       <c r="AX278" t="n">
         <v>10</v>
@@ -34865,13 +34865,13 @@
         <v>10</v>
       </c>
       <c r="W280" t="n">
-        <v>36.38</v>
+        <v>10</v>
       </c>
       <c r="X280" t="n">
-        <v>10</v>
+        <v>30.25</v>
       </c>
       <c r="Y280" t="n">
-        <v>10</v>
+        <v>33.25</v>
       </c>
       <c r="Z280" t="n">
         <v>10</v>
@@ -34883,43 +34883,43 @@
         <v>10</v>
       </c>
       <c r="AC280" t="n">
-        <v>33.83</v>
+        <v>10</v>
       </c>
       <c r="AD280" t="n">
+        <v>45</v>
+      </c>
+      <c r="AE280" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="AF280" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AG280" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AH280" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AI280" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AJ280" t="n">
+        <v>45</v>
+      </c>
+      <c r="AK280" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AL280" t="n">
         <v>10</v>
-      </c>
-      <c r="AE280" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF280" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="AG280" t="n">
-        <v>39.68</v>
-      </c>
-      <c r="AH280" t="n">
-        <v>38.17</v>
-      </c>
-      <c r="AI280" t="n">
-        <v>34.59</v>
-      </c>
-      <c r="AJ280" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK280" t="n">
-        <v>42.08</v>
-      </c>
-      <c r="AL280" t="n">
-        <v>33.92</v>
       </c>
       <c r="AM280" t="n">
         <v>45</v>
       </c>
       <c r="AN280" t="n">
-        <v>45.6</v>
+        <v>45</v>
       </c>
       <c r="AO280" t="n">
-        <v>45</v>
+        <v>39.4</v>
       </c>
       <c r="AP280" t="n">
         <v>45</v>
@@ -34928,19 +34928,19 @@
         <v>45</v>
       </c>
       <c r="AR280" t="n">
+        <v>45</v>
+      </c>
+      <c r="AS280" t="n">
         <v>39.4</v>
       </c>
-      <c r="AS280" t="n">
-        <v>45</v>
-      </c>
       <c r="AT280" t="n">
-        <v>30.72</v>
+        <v>45.12</v>
       </c>
       <c r="AU280" t="n">
-        <v>10</v>
+        <v>37.04</v>
       </c>
       <c r="AV280" t="n">
-        <v>10</v>
+        <v>30.67</v>
       </c>
       <c r="AW280" t="n">
         <v>10</v>
@@ -35291,19 +35291,19 @@
         <v>80</v>
       </c>
       <c r="O283" t="n">
-        <v>82</v>
+        <v>103.75</v>
       </c>
       <c r="P283" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="Q283" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="R283" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="S283" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="T283" t="n">
         <v>125</v>
@@ -35445,19 +35445,19 @@
         <v>80</v>
       </c>
       <c r="O284" t="n">
-        <v>82</v>
+        <v>103.75</v>
       </c>
       <c r="P284" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="Q284" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="R284" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="S284" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="T284" t="n">
         <v>125</v>
@@ -35599,19 +35599,19 @@
         <v>86</v>
       </c>
       <c r="O285" t="n">
-        <v>90.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P285" t="n">
-        <v>91.5</v>
+        <v>95.5</v>
       </c>
       <c r="Q285" t="n">
-        <v>103.5</v>
+        <v>108.5</v>
       </c>
       <c r="R285" t="n">
-        <v>117.5</v>
+        <v>110.5</v>
       </c>
       <c r="S285" t="n">
-        <v>129.5</v>
+        <v>130</v>
       </c>
       <c r="T285" t="n">
         <v>130</v>
@@ -35871,7 +35871,7 @@
         <v>60</v>
       </c>
       <c r="AK287" t="n">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="AL287" t="n">
         <v>15</v>
@@ -36275,7 +36275,7 @@
         <v>50</v>
       </c>
       <c r="O292" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="P292" t="n">
         <v>50</v>
@@ -36633,112 +36633,112 @@
         <v>529</v>
       </c>
       <c r="O295" t="n">
-        <v>537.5</v>
+        <v>553.1</v>
       </c>
       <c r="P295" t="n">
-        <v>548.5</v>
+        <v>562.5</v>
       </c>
       <c r="Q295" t="n">
-        <v>586.5</v>
+        <v>601.5</v>
       </c>
       <c r="R295" t="n">
-        <v>630.5</v>
+        <v>645.5</v>
       </c>
       <c r="S295" t="n">
-        <v>698.5</v>
+        <v>713.42</v>
       </c>
       <c r="T295" t="n">
-        <v>735.52</v>
+        <v>750.52</v>
       </c>
       <c r="U295" t="n">
-        <v>770.55</v>
+        <v>785.55</v>
       </c>
       <c r="V295" t="n">
-        <v>799.42</v>
+        <v>814.42</v>
       </c>
       <c r="W295" t="n">
-        <v>824.38</v>
+        <v>839.38</v>
       </c>
       <c r="X295" t="n">
-        <v>828.25</v>
+        <v>843.25</v>
       </c>
       <c r="Y295" t="n">
-        <v>831.25</v>
+        <v>846.25</v>
       </c>
       <c r="Z295" t="n">
-        <v>824.35</v>
+        <v>839.35</v>
       </c>
       <c r="AA295" t="n">
-        <v>822.5700000000001</v>
+        <v>837.5700000000001</v>
       </c>
       <c r="AB295" t="n">
-        <v>833.45</v>
+        <v>848.45</v>
       </c>
       <c r="AC295" t="n">
-        <v>851.83</v>
+        <v>866.83</v>
       </c>
       <c r="AD295" t="n">
-        <v>867.28</v>
+        <v>882.28</v>
       </c>
       <c r="AE295" t="n">
-        <v>876.99</v>
+        <v>891.99</v>
       </c>
       <c r="AF295" t="n">
-        <v>883.8</v>
+        <v>898.8</v>
       </c>
       <c r="AG295" t="n">
-        <v>882.6799999999999</v>
+        <v>897.6799999999999</v>
       </c>
       <c r="AH295" t="n">
-        <v>881.17</v>
+        <v>896.17</v>
       </c>
       <c r="AI295" t="n">
-        <v>877.59</v>
+        <v>892.59</v>
       </c>
       <c r="AJ295" t="n">
-        <v>868.13</v>
+        <v>883.13</v>
       </c>
       <c r="AK295" t="n">
-        <v>850.1799999999999</v>
+        <v>865.3</v>
       </c>
       <c r="AL295" t="n">
-        <v>842.02</v>
+        <v>857.3</v>
       </c>
       <c r="AM295" t="n">
-        <v>871.3</v>
+        <v>886.5</v>
       </c>
       <c r="AN295" t="n">
-        <v>902</v>
+        <v>917.12</v>
       </c>
       <c r="AO295" t="n">
-        <v>888.4400000000001</v>
+        <v>903</v>
       </c>
       <c r="AP295" t="n">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="AQ295" t="n">
-        <v>861</v>
+        <v>876.15</v>
       </c>
       <c r="AR295" t="n">
-        <v>837.0700000000001</v>
+        <v>852.0700000000001</v>
       </c>
       <c r="AS295" t="n">
-        <v>801.14</v>
+        <v>816.14</v>
       </c>
       <c r="AT295" t="n">
-        <v>763.72</v>
+        <v>778.72</v>
       </c>
       <c r="AU295" t="n">
-        <v>720.04</v>
+        <v>735.04</v>
       </c>
       <c r="AV295" t="n">
-        <v>688.67</v>
+        <v>703.67</v>
       </c>
       <c r="AW295" t="n">
-        <v>650.77</v>
+        <v>665.77</v>
       </c>
       <c r="AX295" t="n">
-        <v>620.53</v>
+        <v>635.53</v>
       </c>
     </row>
     <row r="296">
@@ -36785,112 +36785,112 @@
         <v>804.88</v>
       </c>
       <c r="O296" t="n">
-        <v>817.03</v>
+        <v>833.03</v>
       </c>
       <c r="P296" t="n">
-        <v>832.27</v>
+        <v>846.27</v>
       </c>
       <c r="Q296" t="n">
-        <v>873.88</v>
+        <v>888.88</v>
       </c>
       <c r="R296" t="n">
-        <v>919.55</v>
+        <v>934.55</v>
       </c>
       <c r="S296" t="n">
-        <v>988.64</v>
+        <v>1003.64</v>
       </c>
       <c r="T296" t="n">
-        <v>1026.11</v>
+        <v>1041.11</v>
       </c>
       <c r="U296" t="n">
-        <v>1061.24</v>
+        <v>1076.24</v>
       </c>
       <c r="V296" t="n">
-        <v>1090</v>
+        <v>1105</v>
       </c>
       <c r="W296" t="n">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="X296" t="n">
-        <v>1119</v>
+        <v>1134</v>
       </c>
       <c r="Y296" t="n">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="Z296" t="n">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="AA296" t="n">
-        <v>1113</v>
+        <v>1128</v>
       </c>
       <c r="AB296" t="n">
-        <v>1123.57</v>
+        <v>1138.57</v>
       </c>
       <c r="AC296" t="n">
-        <v>1141.33</v>
+        <v>1156.33</v>
       </c>
       <c r="AD296" t="n">
-        <v>1155.42</v>
+        <v>1170.42</v>
       </c>
       <c r="AE296" t="n">
-        <v>1162.02</v>
+        <v>1177.02</v>
       </c>
       <c r="AF296" t="n">
-        <v>1165</v>
+        <v>1180</v>
       </c>
       <c r="AG296" t="n">
-        <v>1160</v>
+        <v>1175</v>
       </c>
       <c r="AH296" t="n">
-        <v>1155</v>
+        <v>1170</v>
       </c>
       <c r="AI296" t="n">
-        <v>1149.27</v>
+        <v>1164.27</v>
       </c>
       <c r="AJ296" t="n">
-        <v>1138.13</v>
+        <v>1153.13</v>
       </c>
       <c r="AK296" t="n">
-        <v>1120.08</v>
+        <v>1135.08</v>
       </c>
       <c r="AL296" t="n">
-        <v>1111.92</v>
+        <v>1126.92</v>
       </c>
       <c r="AM296" t="n">
-        <v>1141.21</v>
+        <v>1156.21</v>
       </c>
       <c r="AN296" t="n">
-        <v>1172</v>
+        <v>1187</v>
       </c>
       <c r="AO296" t="n">
-        <v>1158</v>
+        <v>1173</v>
       </c>
       <c r="AP296" t="n">
-        <v>1146.56</v>
+        <v>1161.56</v>
       </c>
       <c r="AQ296" t="n">
-        <v>1130.99</v>
+        <v>1145.99</v>
       </c>
       <c r="AR296" t="n">
-        <v>1107.07</v>
+        <v>1122.07</v>
       </c>
       <c r="AS296" t="n">
-        <v>1071.14</v>
+        <v>1086.14</v>
       </c>
       <c r="AT296" t="n">
-        <v>1033.72</v>
+        <v>1048.72</v>
       </c>
       <c r="AU296" t="n">
-        <v>990.04</v>
+        <v>1005.04</v>
       </c>
       <c r="AV296" t="n">
-        <v>958.67</v>
+        <v>973.67</v>
       </c>
       <c r="AW296" t="n">
-        <v>920.77</v>
+        <v>935.77</v>
       </c>
       <c r="AX296" t="n">
-        <v>890.53</v>
+        <v>905.53</v>
       </c>
     </row>
     <row r="297">
@@ -37097,112 +37097,112 @@
         <v>28543.25</v>
       </c>
       <c r="O300" t="n">
-        <v>27974.65</v>
+        <v>27851.92</v>
       </c>
       <c r="P300" t="n">
-        <v>28029.54</v>
+        <v>27951.61</v>
       </c>
       <c r="Q300" t="n">
-        <v>29163.66</v>
+        <v>29028.35</v>
       </c>
       <c r="R300" t="n">
-        <v>30175.64</v>
+        <v>30120.53</v>
       </c>
       <c r="S300" t="n">
-        <v>31144.38</v>
+        <v>31113.02</v>
       </c>
       <c r="T300" t="n">
-        <v>31773.17</v>
+        <v>31719.67</v>
       </c>
       <c r="U300" t="n">
-        <v>32198.94</v>
+        <v>32148.55</v>
       </c>
       <c r="V300" t="n">
-        <v>32512.19</v>
+        <v>32483.89</v>
       </c>
       <c r="W300" t="n">
-        <v>32723.6</v>
+        <v>32718.29</v>
       </c>
       <c r="X300" t="n">
-        <v>32766.62</v>
+        <v>32759.31</v>
       </c>
       <c r="Y300" t="n">
-        <v>32549.27</v>
+        <v>32524.4</v>
       </c>
       <c r="Z300" t="n">
-        <v>31757.08</v>
+        <v>31726.77</v>
       </c>
       <c r="AA300" t="n">
-        <v>31673.98</v>
+        <v>31622.37</v>
       </c>
       <c r="AB300" t="n">
-        <v>32558.43</v>
+        <v>32519.16</v>
       </c>
       <c r="AC300" t="n">
-        <v>33718.38</v>
+        <v>33717.21</v>
       </c>
       <c r="AD300" t="n">
-        <v>33877.01</v>
+        <v>33854.72</v>
       </c>
       <c r="AE300" t="n">
-        <v>33912.29</v>
+        <v>33919.43</v>
       </c>
       <c r="AF300" t="n">
-        <v>33868.13</v>
+        <v>33877.74</v>
       </c>
       <c r="AG300" t="n">
-        <v>33846.04</v>
+        <v>33863.61</v>
       </c>
       <c r="AH300" t="n">
-        <v>33488.77</v>
+        <v>33458.16</v>
       </c>
       <c r="AI300" t="n">
-        <v>33223.54</v>
+        <v>33188.75</v>
       </c>
       <c r="AJ300" t="n">
-        <v>33053.51</v>
+        <v>33013.64</v>
       </c>
       <c r="AK300" t="n">
-        <v>33669.62</v>
+        <v>33632.18</v>
       </c>
       <c r="AL300" t="n">
-        <v>34697.01</v>
+        <v>34670.28</v>
       </c>
       <c r="AM300" t="n">
-        <v>34484.93</v>
+        <v>34455.75</v>
       </c>
       <c r="AN300" t="n">
-        <v>34138.88</v>
+        <v>34104.63</v>
       </c>
       <c r="AO300" t="n">
-        <v>33951.41</v>
+        <v>33915.35</v>
       </c>
       <c r="AP300" t="n">
-        <v>33659.44</v>
+        <v>33621.4</v>
       </c>
       <c r="AQ300" t="n">
-        <v>33352.35</v>
+        <v>33311.98</v>
       </c>
       <c r="AR300" t="n">
-        <v>32911.02</v>
+        <v>32868.91</v>
       </c>
       <c r="AS300" t="n">
-        <v>32206.36</v>
+        <v>32162.71</v>
       </c>
       <c r="AT300" t="n">
-        <v>31502.47</v>
+        <v>31451.46</v>
       </c>
       <c r="AU300" t="n">
-        <v>30867.5</v>
+        <v>30812.12</v>
       </c>
       <c r="AV300" t="n">
-        <v>30165.01</v>
+        <v>30104.25</v>
       </c>
       <c r="AW300" t="n">
-        <v>29659.55</v>
+        <v>29593.99</v>
       </c>
       <c r="AX300" t="n">
-        <v>29184.32</v>
+        <v>29111.51</v>
       </c>
     </row>
     <row r="301">
